--- a/document/成果物ドキュメント_コメント投稿機能.xlsx
+++ b/document/成果物ドキュメント_コメント投稿機能.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskManager62\document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER124\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA569131-AFC2-4623-AF55-F6CF08D63C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828B4931-553A-45E1-9D80-4A6B9409509C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,23 +18,21 @@
     <sheet name="画面遷移図" sheetId="3" r:id="rId3"/>
     <sheet name="詳細クラス図" sheetId="4" r:id="rId4"/>
     <sheet name="画面設計書 (コメント投稿画面)" sheetId="5" r:id="rId5"/>
-    <sheet name="画面設計書 (コメント投稿エラー画面)" sheetId="7" r:id="rId6"/>
-    <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId7"/>
+    <sheet name="画面設計書 (コメント投稿完了画面) " sheetId="8" r:id="rId6"/>
+    <sheet name="画面設計書 (コメント投稿エラー画面)" sheetId="7" r:id="rId7"/>
+    <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="99">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
   <si>
     <t>初版</t>
-  </si>
-  <si>
-    <t>YYYY/MM/DD</t>
   </si>
   <si>
     <t>ユースケース記述</t>
@@ -252,32 +250,11 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>コメント投稿機能</t>
-    <rPh sb="4" eb="6">
-      <t>トウコウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>キノウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>コメントを投稿できる</t>
-    <rPh sb="5" eb="7">
-      <t>トウコウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>商品企画部の従業員(ユーザー)</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>ユーザーがシステムにログインしていること</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>なし</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -309,39 +286,12 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>投稿</t>
-    <rPh sb="0" eb="2">
-      <t>トウコウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>コメント投稿エラー画面</t>
     <rPh sb="4" eb="6">
       <t>トウコウ</t>
     </rPh>
     <rPh sb="9" eb="11">
       <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>コメント投稿画面へ戻る</t>
-    <rPh sb="4" eb="8">
-      <t>トウコウガメン</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>モド</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>コメント投稿へ戻る</t>
-    <rPh sb="4" eb="6">
-      <t>トウコウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>モド</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -354,44 +304,9 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>システムはユーザーが入力したコメントをDBに登録すること</t>
-    <rPh sb="10" eb="12">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>チーム名 62期</t>
     <rPh sb="7" eb="8">
       <t>キ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>1.ユーザーがコメントを入力する
-2.ユーザーが投稿を選択する
-3.システムがコメントを登録する
-4.システムがコメント投稿完了画面を表示する</t>
-    <rPh sb="12" eb="14">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>トウコウ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="60" eb="66">
-      <t>トウコウカンリョウガメン</t>
-    </rPh>
-    <rPh sb="67" eb="69">
-      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -403,11 +318,183 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>投稿</t>
+    <t>コメントを投稿する</t>
+    <rPh sb="5" eb="7">
+      <t>トウコウ</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>テキストボックス</t>
+    <t>システムに対象のタスクへのコメントを登録する</t>
+    <rPh sb="5" eb="7">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.ユーザーがタスク詳細画面でコメントの投稿を選択する
+2.システムがコメント投稿画面を表示する
+3.ユーザーがコメントを入力する
+4.ユーザーがコメントの投稿を確定する
+5.システムが入力された内容と現在日時をデータベースに登録する
+6.システムがコメント投稿完了画面を表示する</t>
+    <rPh sb="10" eb="14">
+      <t>ショウサイガメン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>トウコウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>トウコウ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>トウコウ</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>カクテイ</t>
+    </rPh>
+    <rPh sb="93" eb="95">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="101" eb="105">
+      <t>ゲンザイニチジ</t>
+    </rPh>
+    <rPh sb="113" eb="115">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="129" eb="135">
+      <t>トウコウカンリョウガメン</t>
+    </rPh>
+    <rPh sb="136" eb="138">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>3a1．ユーザーがコメントの投稿を中止し、直前の画面に戻る
+3a2．システムがタスク詳細画面を表示する</t>
+    <rPh sb="14" eb="16">
+      <t>トウコウ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>6a．システムがコメントの登録に失敗した場合
+6a1．システムがコメント投稿エラー画面を表示する</t>
+    <rPh sb="13" eb="15">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>トウコウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>対象のコメントがデータベースに登録されていること</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>コメント投稿画面</t>
+    <rPh sb="4" eb="6">
+      <t>トウコウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>投稿する</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>投稿する</t>
+    <rPh sb="0" eb="2">
+      <t>トウコウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>入力必須、最大100文字</t>
+    <rPh sb="0" eb="4">
+      <t>ニュウリョクヒッス</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイダイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>モジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>コメント投稿完了画面</t>
+    <rPh sb="4" eb="6">
+      <t>トウコウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>メニュー画面へ</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>メニュー画面へ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>menu.jsp</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>コメント投稿画面へ</t>
+    <rPh sb="4" eb="8">
+      <t>トウコウガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>コメント投稿画面へ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>GET</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1169,7 +1256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1287,7 +1374,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1296,16 +1383,106 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1314,52 +1491,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1374,95 +1506,56 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1470,23 +1563,20 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1575,23 +1665,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>312965</xdr:colOff>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>155863</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>115778</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>163286</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>20712</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{381A6AFF-BFE1-6611-72FB-CF1F00DD0454}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5328A1BE-8E67-2342-8335-403D27FB135F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1614,8 +1704,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="346364" y="1056409"/>
-          <a:ext cx="9195954" cy="8688278"/>
+          <a:off x="993322" y="925286"/>
+          <a:ext cx="6885214" cy="4592712"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1642,22 +1732,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>828675</xdr:colOff>
+      <xdr:colOff>861432</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>28802</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>29090</xdr:rowOff>
+      <xdr:colOff>317810</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>169360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D50C7CD-8053-4CCC-AA2A-6574DB1D3832}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B832168B-A850-FF1B-7373-59BBDDDC7B98}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1680,8 +1770,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2971800" y="1543050"/>
-          <a:ext cx="3019425" cy="1876940"/>
+          <a:off x="3021981" y="1585326"/>
+          <a:ext cx="2801744" cy="1743546"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1708,22 +1798,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>257175</xdr:rowOff>
+      <xdr:colOff>333374</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:colOff>647699</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>199757</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B49CAB9B-D081-F065-4865-DC1F1852F2D0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CD3B8B0-D5C5-4A3A-86C9-9320AFE6F922}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1746,8 +1836,74 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2181225" y="1533525"/>
-          <a:ext cx="4400550" cy="1885950"/>
+          <a:off x="2676524" y="1581150"/>
+          <a:ext cx="4181475" cy="1761857"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>672084</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15B63920-C432-3297-B4E9-F52BF5478F92}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2609850" y="1552575"/>
+          <a:ext cx="4272534" cy="1800225"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1976,85 +2132,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="77" t="s">
+      <c r="C2" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
-      <c r="O2" s="78"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
-      <c r="L3" s="58"/>
-      <c r="M3" s="58"/>
-      <c r="N3" s="58"/>
-      <c r="O3" s="58"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="58"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="58"/>
-      <c r="L5" s="58"/>
-      <c r="M5" s="58"/>
-      <c r="N5" s="58"/>
-      <c r="O5" s="58"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="43"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="58"/>
-      <c r="M6" s="58"/>
-      <c r="N6" s="58"/>
-      <c r="O6" s="58"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2074,44 +2230,44 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="79" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="58"/>
-      <c r="K8" s="58"/>
-      <c r="L8" s="58"/>
-      <c r="M8" s="58"/>
+      <c r="E8" s="46" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
+      <c r="L8" s="43"/>
+      <c r="M8" s="43"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="75" t="s">
+      <c r="G13" s="39" t="s">
         <v>1</v>
       </c>
       <c r="H13" s="41"/>
-      <c r="I13" s="75" t="s">
-        <v>2</v>
+      <c r="I13" s="106">
+        <v>46129</v>
       </c>
       <c r="J13" s="40"/>
       <c r="K13" s="41"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="75"/>
+      <c r="G14" s="39"/>
       <c r="H14" s="41"/>
-      <c r="I14" s="75"/>
+      <c r="I14" s="39"/>
       <c r="J14" s="40"/>
       <c r="K14" s="41"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="75"/>
+      <c r="G15" s="39"/>
       <c r="H15" s="41"/>
-      <c r="I15" s="75"/>
+      <c r="I15" s="39"/>
       <c r="J15" s="40"/>
       <c r="K15" s="41"/>
     </row>
@@ -2122,13 +2278,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="76" t="s">
-        <v>88</v>
-      </c>
-      <c r="H17" s="58"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="58"/>
-      <c r="K17" s="58"/>
+      <c r="G17" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3142,194 +3298,194 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="58" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="59"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="64" t="s">
+      <c r="E1" s="67"/>
+      <c r="F1" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="64" t="s">
+      <c r="G1" s="67"/>
+      <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="61"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="80" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="81"/>
+      <c r="F2" s="80" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="81"/>
+      <c r="H2" s="84">
+        <v>46122</v>
+      </c>
+      <c r="I2" s="73" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="76"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="61"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="78"/>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A5" s="66" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="57"/>
-      <c r="B2" s="58"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="65" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="66"/>
-      <c r="F2" s="65" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2" s="66"/>
-      <c r="H2" s="68">
-        <v>46122</v>
-      </c>
-      <c r="I2" s="44" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="46"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="57"/>
-      <c r="B3" s="58"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="47"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="81"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="83"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="90" t="s">
+      <c r="B5" s="51"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="52"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="68" t="s">
         <v>9</v>
-      </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="94" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="52"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="85" t="s">
-        <v>10</v>
       </c>
       <c r="B6" s="40"/>
       <c r="C6" s="41"/>
-      <c r="D6" s="42" t="s">
-        <v>70</v>
+      <c r="D6" s="53" t="s">
+        <v>83</v>
       </c>
       <c r="E6" s="40"/>
       <c r="F6" s="40"/>
       <c r="G6" s="40"/>
       <c r="H6" s="40"/>
       <c r="I6" s="40"/>
-      <c r="J6" s="43"/>
+      <c r="J6" s="54"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="85" t="s">
-        <v>11</v>
+      <c r="A7" s="68" t="s">
+        <v>10</v>
       </c>
       <c r="B7" s="40"/>
       <c r="C7" s="41"/>
-      <c r="D7" s="42" t="s">
-        <v>71</v>
+      <c r="D7" s="53" t="s">
+        <v>68</v>
       </c>
       <c r="E7" s="40"/>
       <c r="F7" s="40"/>
       <c r="G7" s="40"/>
       <c r="H7" s="40"/>
       <c r="I7" s="40"/>
-      <c r="J7" s="43"/>
+      <c r="J7" s="54"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="85" t="s">
-        <v>12</v>
+      <c r="A8" s="68" t="s">
+        <v>11</v>
       </c>
       <c r="B8" s="40"/>
       <c r="C8" s="41"/>
-      <c r="D8" s="42" t="s">
-        <v>72</v>
+      <c r="D8" s="53" t="s">
+        <v>69</v>
       </c>
       <c r="E8" s="40"/>
       <c r="F8" s="40"/>
       <c r="G8" s="40"/>
       <c r="H8" s="40"/>
       <c r="I8" s="40"/>
-      <c r="J8" s="43"/>
+      <c r="J8" s="54"/>
     </row>
     <row r="9" spans="1:10" ht="87.75" customHeight="1">
-      <c r="A9" s="91" t="s">
+      <c r="A9" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="84" t="s">
-        <v>14</v>
-      </c>
       <c r="C9" s="41"/>
-      <c r="D9" s="95" t="s">
-        <v>89</v>
+      <c r="D9" s="55" t="s">
+        <v>84</v>
       </c>
       <c r="E9" s="40"/>
       <c r="F9" s="40"/>
       <c r="G9" s="40"/>
       <c r="H9" s="40"/>
       <c r="I9" s="40"/>
-      <c r="J9" s="43"/>
+      <c r="J9" s="54"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="92"/>
-      <c r="B10" s="84" t="s">
-        <v>15</v>
+      <c r="A10" s="70"/>
+      <c r="B10" s="72" t="s">
+        <v>14</v>
       </c>
       <c r="C10" s="41"/>
-      <c r="D10" s="42" t="s">
-        <v>73</v>
+      <c r="D10" s="55" t="s">
+        <v>85</v>
       </c>
       <c r="E10" s="40"/>
       <c r="F10" s="40"/>
       <c r="G10" s="40"/>
       <c r="H10" s="40"/>
       <c r="I10" s="40"/>
-      <c r="J10" s="43"/>
+      <c r="J10" s="54"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="93"/>
-      <c r="B11" s="84" t="s">
-        <v>16</v>
+      <c r="A11" s="71"/>
+      <c r="B11" s="72" t="s">
+        <v>15</v>
       </c>
       <c r="C11" s="41"/>
-      <c r="D11" s="42" t="s">
-        <v>73</v>
+      <c r="D11" s="55" t="s">
+        <v>86</v>
       </c>
       <c r="E11" s="40"/>
       <c r="F11" s="40"/>
       <c r="G11" s="40"/>
       <c r="H11" s="40"/>
       <c r="I11" s="40"/>
-      <c r="J11" s="43"/>
+      <c r="J11" s="54"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="85" t="s">
-        <v>17</v>
+      <c r="A12" s="68" t="s">
+        <v>16</v>
       </c>
       <c r="B12" s="40"/>
       <c r="C12" s="41"/>
-      <c r="D12" s="42" t="s">
+      <c r="D12" s="53" t="s">
         <v>87</v>
       </c>
       <c r="E12" s="40"/>
@@ -3337,21 +3493,21 @@
       <c r="G12" s="40"/>
       <c r="H12" s="40"/>
       <c r="I12" s="40"/>
-      <c r="J12" s="43"/>
+      <c r="J12" s="54"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="86" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="71"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="74"/>
+      <c r="A13" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="48"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="49"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4342,6 +4498,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -4350,25 +4525,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4387,72 +4543,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="64" t="s">
+      <c r="A1" s="85" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="59"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="67"/>
+      <c r="F1" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="64" t="s">
+      <c r="G1" s="67"/>
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>8</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="57"/>
-      <c r="B2" s="58"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="65" t="s">
+      <c r="A2" s="61"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="80" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="81"/>
+      <c r="F2" s="80" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="66"/>
-      <c r="F2" s="65" t="s">
+      <c r="G2" s="81"/>
+      <c r="H2" s="84">
+        <v>46120</v>
+      </c>
+      <c r="I2" s="73" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="66"/>
-      <c r="H2" s="68">
-        <v>46120</v>
-      </c>
-      <c r="I2" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" s="46"/>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="57"/>
-      <c r="B3" s="58"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="47"/>
+      <c r="A3" s="61"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="81"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="83"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="78"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -5806,72 +5962,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="60" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="64" t="s">
+      <c r="A1" s="85" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="59"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="67"/>
+      <c r="F1" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="64" t="s">
+      <c r="G1" s="67"/>
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>8</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="57"/>
-      <c r="B2" s="58"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="65" t="s">
+      <c r="A2" s="61"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="80" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="81"/>
+      <c r="F2" s="80" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="66"/>
-      <c r="F2" s="65" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2" s="66"/>
-      <c r="H2" s="68">
+      <c r="G2" s="81"/>
+      <c r="H2" s="84">
         <v>46125</v>
       </c>
-      <c r="I2" s="44" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="46"/>
+      <c r="I2" s="73" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="76"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="57"/>
-      <c r="B3" s="58"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="47"/>
+      <c r="A3" s="61"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="81"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="83"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="78"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7220,92 +7376,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="85" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="59"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="67"/>
+      <c r="F1" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="67"/>
+      <c r="H1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="61"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="80" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="81"/>
+      <c r="F2" s="80" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="81"/>
+      <c r="H2" s="84">
+        <v>46122</v>
+      </c>
+      <c r="I2" s="73" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="76"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="61"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="61"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="64" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="64" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="57"/>
-      <c r="B2" s="58"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="65" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="66"/>
-      <c r="F2" s="65" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2" s="66"/>
-      <c r="H2" s="68">
-        <v>46122</v>
-      </c>
-      <c r="I2" s="44" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="46"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="57"/>
-      <c r="B3" s="58"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="47"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="57"/>
-      <c r="B4" s="58"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="47"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="48" t="s">
+      <c r="B5" s="51"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="90" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="52"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="89" t="s">
         <v>22</v>
-      </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="51" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="52"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="53" t="s">
-        <v>23</v>
       </c>
       <c r="B6" s="40"/>
       <c r="C6" s="40"/>
@@ -7315,95 +7471,95 @@
       <c r="G6" s="40"/>
       <c r="H6" s="40"/>
       <c r="I6" s="40"/>
-      <c r="J6" s="43"/>
+      <c r="J6" s="54"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="54"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="56"/>
+      <c r="A7" s="91"/>
+      <c r="B7" s="92"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="92"/>
+      <c r="F7" s="92"/>
+      <c r="G7" s="92"/>
+      <c r="H7" s="92"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="93"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="57"/>
-      <c r="B8" s="58"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="59"/>
+      <c r="A8" s="61"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="94"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="57"/>
-      <c r="B9" s="58"/>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="59"/>
+      <c r="A9" s="61"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="94"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="57"/>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58"/>
-      <c r="H10" s="58"/>
-      <c r="I10" s="58"/>
-      <c r="J10" s="59"/>
+      <c r="A10" s="61"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="94"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="57"/>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="59"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="94"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="57"/>
-      <c r="B12" s="58"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="59"/>
+      <c r="A12" s="61"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="94"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="57"/>
-      <c r="B13" s="58"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="59"/>
+      <c r="A13" s="61"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="94"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="53" t="s">
-        <v>24</v>
+      <c r="A14" s="89" t="s">
+        <v>23</v>
       </c>
       <c r="B14" s="40"/>
       <c r="C14" s="40"/>
@@ -7413,153 +7569,153 @@
       <c r="G14" s="40"/>
       <c r="H14" s="40"/>
       <c r="I14" s="40"/>
-      <c r="J14" s="43"/>
+      <c r="J14" s="54"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="53" t="s">
-        <v>25</v>
+      <c r="A15" s="89" t="s">
+        <v>24</v>
       </c>
       <c r="B15" s="40"/>
       <c r="C15" s="41"/>
-      <c r="D15" s="42" t="s">
-        <v>85</v>
+      <c r="D15" s="53" t="s">
+        <v>78</v>
       </c>
       <c r="E15" s="40"/>
       <c r="F15" s="40"/>
       <c r="G15" s="40"/>
       <c r="H15" s="41"/>
       <c r="I15" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="89" t="s">
         <v>26</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="53" t="s">
-        <v>27</v>
       </c>
       <c r="B16" s="40"/>
       <c r="C16" s="41"/>
       <c r="D16" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="F16" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="G16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="69" t="s">
-        <v>18</v>
+      <c r="H16" s="95" t="s">
+        <v>17</v>
       </c>
       <c r="I16" s="40"/>
-      <c r="J16" s="43"/>
+      <c r="J16" s="54"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="39" t="s">
-        <v>76</v>
+      <c r="A17" s="86" t="s">
+        <v>72</v>
       </c>
       <c r="B17" s="40"/>
       <c r="C17" s="41"/>
       <c r="D17" s="17" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G17" s="18"/>
-      <c r="H17" s="42" t="s">
-        <v>92</v>
+      <c r="H17" s="53" t="s">
+        <v>91</v>
       </c>
       <c r="I17" s="40"/>
-      <c r="J17" s="43"/>
+      <c r="J17" s="54"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="39" t="s">
-        <v>79</v>
+      <c r="A18" s="86" t="s">
+        <v>75</v>
       </c>
       <c r="B18" s="40"/>
       <c r="C18" s="41"/>
       <c r="D18" s="17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F18" s="18"/>
       <c r="G18" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="H18" s="42"/>
+        <v>90</v>
+      </c>
+      <c r="H18" s="53"/>
       <c r="I18" s="40"/>
-      <c r="J18" s="43"/>
+      <c r="J18" s="54"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="39"/>
+      <c r="A19" s="86"/>
       <c r="B19" s="40"/>
       <c r="C19" s="41"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="42"/>
+      <c r="H19" s="53"/>
       <c r="I19" s="40"/>
-      <c r="J19" s="43"/>
+      <c r="J19" s="54"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="39"/>
+      <c r="A20" s="86"/>
       <c r="B20" s="40"/>
       <c r="C20" s="41"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="42"/>
+      <c r="H20" s="53"/>
       <c r="I20" s="40"/>
-      <c r="J20" s="43"/>
+      <c r="J20" s="54"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="39"/>
+      <c r="A21" s="86"/>
       <c r="B21" s="40"/>
       <c r="C21" s="41"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="42"/>
+      <c r="H21" s="53"/>
       <c r="I21" s="40"/>
-      <c r="J21" s="43"/>
+      <c r="J21" s="54"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="39"/>
+      <c r="A22" s="86"/>
       <c r="B22" s="40"/>
       <c r="C22" s="41"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="42"/>
+      <c r="H22" s="53"/>
       <c r="I22" s="40"/>
-      <c r="J22" s="43"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="70"/>
-      <c r="B23" s="71"/>
-      <c r="C23" s="72"/>
+      <c r="J22" s="54"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A23" s="88"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="57"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="71"/>
-      <c r="J23" s="74"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="49"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8540,16 +8696,11 @@
     <row r="1000" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8566,11 +8717,16 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8580,7 +8736,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F27D4FC-0523-4E2E-B4A2-954E5C9745F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{305952F0-5380-483E-AA53-3AD01E83CB41}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -8596,92 +8752,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="85" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="59"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="67"/>
+      <c r="F1" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="67"/>
+      <c r="H1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="61"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="80" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="81"/>
+      <c r="F2" s="80" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="81"/>
+      <c r="H2" s="84">
+        <v>46122</v>
+      </c>
+      <c r="I2" s="73" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="76"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="61"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="61"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="64" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="64" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="57"/>
-      <c r="B2" s="58"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="65" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="66"/>
-      <c r="F2" s="65" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2" s="66"/>
-      <c r="H2" s="68">
-        <v>46122</v>
-      </c>
-      <c r="I2" s="44" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="46"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="57"/>
-      <c r="B3" s="58"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="47"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="57"/>
-      <c r="B4" s="58"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="47"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="48" t="s">
+      <c r="B5" s="51"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="90" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="52"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="89" t="s">
         <v>22</v>
-      </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="52"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="53" t="s">
-        <v>23</v>
       </c>
       <c r="B6" s="40"/>
       <c r="C6" s="40"/>
@@ -8691,95 +8847,95 @@
       <c r="G6" s="40"/>
       <c r="H6" s="40"/>
       <c r="I6" s="40"/>
-      <c r="J6" s="43"/>
+      <c r="J6" s="54"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="54"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="56"/>
+      <c r="A7" s="91"/>
+      <c r="B7" s="92"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="92"/>
+      <c r="F7" s="92"/>
+      <c r="G7" s="92"/>
+      <c r="H7" s="92"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="93"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="57"/>
-      <c r="B8" s="58"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="59"/>
+      <c r="A8" s="61"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="94"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="57"/>
-      <c r="B9" s="58"/>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="59"/>
+      <c r="A9" s="61"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="94"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="57"/>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58"/>
-      <c r="H10" s="58"/>
-      <c r="I10" s="58"/>
-      <c r="J10" s="59"/>
+      <c r="A10" s="61"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="94"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="57"/>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="59"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="94"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="57"/>
-      <c r="B12" s="58"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="59"/>
+      <c r="A12" s="61"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="94"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="57"/>
-      <c r="B13" s="58"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="59"/>
+      <c r="A13" s="61"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="94"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="53" t="s">
-        <v>24</v>
+      <c r="A14" s="89" t="s">
+        <v>23</v>
       </c>
       <c r="B14" s="40"/>
       <c r="C14" s="40"/>
@@ -8789,143 +8945,143 @@
       <c r="G14" s="40"/>
       <c r="H14" s="40"/>
       <c r="I14" s="40"/>
-      <c r="J14" s="43"/>
+      <c r="J14" s="54"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="53" t="s">
-        <v>25</v>
+      <c r="A15" s="89" t="s">
+        <v>24</v>
       </c>
       <c r="B15" s="40"/>
       <c r="C15" s="41"/>
-      <c r="D15" s="42" t="s">
-        <v>86</v>
+      <c r="D15" s="53" t="s">
+        <v>95</v>
       </c>
       <c r="E15" s="40"/>
       <c r="F15" s="40"/>
       <c r="G15" s="40"/>
       <c r="H15" s="41"/>
       <c r="I15" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="89" t="s">
         <v>26</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="53" t="s">
-        <v>27</v>
       </c>
       <c r="B16" s="40"/>
       <c r="C16" s="41"/>
       <c r="D16" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="F16" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="G16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="69" t="s">
-        <v>18</v>
+      <c r="H16" s="95" t="s">
+        <v>17</v>
       </c>
       <c r="I16" s="40"/>
-      <c r="J16" s="43"/>
+      <c r="J16" s="54"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="39" t="s">
-        <v>76</v>
+      <c r="A17" s="86" t="s">
+        <v>72</v>
       </c>
       <c r="B17" s="40"/>
       <c r="C17" s="41"/>
       <c r="D17" s="17" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="H17" s="42"/>
+        <v>94</v>
+      </c>
+      <c r="H17" s="53"/>
       <c r="I17" s="40"/>
-      <c r="J17" s="43"/>
+      <c r="J17" s="54"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="39"/>
+      <c r="A18" s="86"/>
       <c r="B18" s="40"/>
       <c r="C18" s="41"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="42"/>
+      <c r="H18" s="53"/>
       <c r="I18" s="40"/>
-      <c r="J18" s="43"/>
+      <c r="J18" s="54"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="39"/>
+      <c r="A19" s="86"/>
       <c r="B19" s="40"/>
       <c r="C19" s="41"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="42"/>
+      <c r="H19" s="53"/>
       <c r="I19" s="40"/>
-      <c r="J19" s="43"/>
+      <c r="J19" s="54"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="39"/>
+      <c r="A20" s="86"/>
       <c r="B20" s="40"/>
       <c r="C20" s="41"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="42"/>
+      <c r="H20" s="53"/>
       <c r="I20" s="40"/>
-      <c r="J20" s="43"/>
+      <c r="J20" s="54"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="39"/>
+      <c r="A21" s="86"/>
       <c r="B21" s="40"/>
       <c r="C21" s="41"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="42"/>
+      <c r="H21" s="53"/>
       <c r="I21" s="40"/>
-      <c r="J21" s="43"/>
+      <c r="J21" s="54"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="39"/>
+      <c r="A22" s="86"/>
       <c r="B22" s="40"/>
       <c r="C22" s="41"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="42"/>
+      <c r="H22" s="53"/>
       <c r="I22" s="40"/>
-      <c r="J22" s="43"/>
+      <c r="J22" s="54"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="70"/>
-      <c r="B23" s="71"/>
-      <c r="C23" s="72"/>
+      <c r="A23" s="88"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="57"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="71"/>
-      <c r="J23" s="74"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="49"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9906,21 +10062,23 @@
     <row r="1000" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="I2:I4"/>
@@ -9935,8 +10093,6 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9946,6 +10102,1372 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F27D4FC-0523-4E2E-B4A2-954E5C9745F3}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="3" width="5.140625" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="16.7109375" customWidth="1"/>
+    <col min="11" max="26" width="8.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="18" customHeight="1">
+      <c r="A1" s="85" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="59"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="67"/>
+      <c r="F1" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="67"/>
+      <c r="H1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="61"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="80" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="81"/>
+      <c r="F2" s="80" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="81"/>
+      <c r="H2" s="84">
+        <v>46122</v>
+      </c>
+      <c r="I2" s="73" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="76"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="61"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="77"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="61"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="77"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="87" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="51"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="90" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="52"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="89" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="54"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="91"/>
+      <c r="B7" s="92"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="92"/>
+      <c r="F7" s="92"/>
+      <c r="G7" s="92"/>
+      <c r="H7" s="92"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="93"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="61"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="94"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="61"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="94"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="61"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="94"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="61"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="94"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="61"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="94"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A13" s="61"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="94"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="89" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="54"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="89" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="40"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="53" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="89" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="95" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="40"/>
+      <c r="J16" s="54"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A17" s="86" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="40"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="H17" s="53"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="54"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A18" s="86"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="54"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="86"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="54"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="86"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="54"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="86"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="54"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="86"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="54"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A23" s="88"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="49"/>
+    </row>
+    <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="33" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="34" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="35" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="36" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="37" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="38" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="39" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="40" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="41" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="42" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="43" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="44" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="45" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="46" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="47" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="48" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="49" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="50" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="51" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="52" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="53" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="54" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="55" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="56" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="57" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="58" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="59" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="60" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="61" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="62" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="63" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="64" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="65" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="66" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="67" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="68" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="69" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="70" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="71" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="72" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="73" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="74" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="75" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="76" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="77" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="78" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="79" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="80" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="81" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="82" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="83" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="84" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="85" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="86" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="87" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="88" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="89" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="90" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="91" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="92" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="93" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="94" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="95" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="96" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="97" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="98" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="99" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="100" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="101" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="102" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="103" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="104" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="105" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="106" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="107" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="108" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="109" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="110" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="111" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="112" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="113" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="114" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="115" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="116" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="117" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="118" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="119" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="120" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="121" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="122" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="123" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="124" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="125" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="126" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="127" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="128" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="129" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="130" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="131" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="132" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="133" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="134" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="135" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="136" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="137" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="138" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="139" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="140" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="141" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="142" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="143" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="144" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="145" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="146" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="147" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="148" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="149" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="150" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="151" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="152" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="153" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="154" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="155" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="156" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="157" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="158" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="159" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="160" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="161" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="162" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="163" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="164" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="165" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="166" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="167" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="168" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="169" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="170" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="171" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="172" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="173" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="174" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="175" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="176" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="177" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="178" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="179" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="180" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="181" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="182" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="183" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="184" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="185" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="186" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="187" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="188" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="189" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="190" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="191" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="192" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="193" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="194" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="195" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="196" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="197" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="198" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="199" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="200" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="201" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="202" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="203" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="204" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="205" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="206" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="207" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="208" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="209" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="210" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="211" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="212" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="213" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="214" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="215" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="216" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="217" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="218" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="219" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="220" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="221" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="222" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="223" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="224" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="225" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="226" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="227" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="228" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="229" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="230" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="231" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="232" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="233" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="234" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="235" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="236" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="237" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="238" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="239" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="240" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="241" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="242" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="243" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="244" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="245" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="246" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="247" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="248" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="249" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="250" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="251" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="252" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="253" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="254" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="255" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="256" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="257" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="258" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="259" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="260" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="261" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="262" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="263" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="264" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="265" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="266" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="267" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="268" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="269" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="270" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="271" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="272" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="273" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="274" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="275" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="276" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="277" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="278" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="279" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="280" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="281" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="282" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="283" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="284" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="285" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="286" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="287" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="288" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="289" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="290" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="291" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="292" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="293" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="294" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="295" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="296" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="297" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="298" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="299" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="300" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="301" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="302" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="303" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="304" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="305" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="306" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="307" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="308" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="309" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="310" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="311" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="312" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="313" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="314" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="315" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="316" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="317" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="318" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="319" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="320" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="321" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="322" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="323" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="324" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="325" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="326" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="327" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="328" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="329" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="330" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="331" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="332" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="333" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="334" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="335" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="336" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="337" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="338" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="339" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="340" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="341" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="342" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="343" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="344" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="345" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="346" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="347" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="348" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="349" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="350" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="351" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="352" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="353" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="354" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="355" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="356" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="357" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="358" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="359" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="360" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="361" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="362" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="363" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="364" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="365" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="366" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="367" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="368" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="369" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="370" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="371" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="372" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="373" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="374" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="375" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="376" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="377" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="378" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="379" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="380" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="381" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="382" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="383" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="384" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="385" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="386" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="387" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="388" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="389" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="390" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="391" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="392" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="393" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="394" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="395" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="396" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="397" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="398" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="399" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="400" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="401" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="402" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="403" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="404" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="405" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="406" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="407" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="408" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="409" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="410" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="411" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="412" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="413" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="414" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="415" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="416" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="417" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="418" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="419" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="420" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="421" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="422" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="423" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="424" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="425" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="426" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="427" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="428" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="429" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="430" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="431" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="432" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="433" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="434" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="435" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="436" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="437" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="438" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="439" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="440" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="441" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="442" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="443" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="444" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="445" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="446" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="447" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="448" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="449" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="450" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="451" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="452" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="453" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="454" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="455" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="456" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="457" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="458" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="459" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="460" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="461" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="462" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="463" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="464" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="465" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="466" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="467" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="468" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="469" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="470" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="471" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="472" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="473" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="474" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="475" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="476" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="477" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="478" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="479" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="480" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="481" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="482" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="483" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="484" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="485" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="486" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="487" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="488" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="489" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="490" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="491" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="492" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="493" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="494" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="495" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="496" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="497" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="498" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="499" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="500" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="501" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="502" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="503" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="504" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="505" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="506" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="507" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="508" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="509" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="510" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="511" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="512" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="513" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="514" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="515" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="516" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="517" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="518" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="519" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="520" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="521" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="522" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="523" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="524" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="525" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="526" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="527" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="528" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="529" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="530" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="531" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="532" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="533" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="534" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="535" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="536" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="537" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="538" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="539" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="540" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="541" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="542" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="543" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="544" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="545" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="546" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="547" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="548" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="549" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="550" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="551" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="552" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="553" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="554" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="555" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="556" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="557" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="558" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="559" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="560" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="561" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="562" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="563" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="564" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="565" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="566" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="567" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="568" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="569" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="570" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="571" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="572" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="573" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="574" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="575" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="576" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="577" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="578" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="579" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="580" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="581" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="582" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="583" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="584" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="585" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="586" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="587" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="588" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="589" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="590" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="591" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="592" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="593" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="594" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="595" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="596" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="597" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="598" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="599" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="600" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="601" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="602" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="603" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="604" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="605" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="606" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="607" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="608" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="609" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="610" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="611" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="612" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="613" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="614" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="615" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="616" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="617" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="618" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="619" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="620" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="621" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="622" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="623" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="624" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="625" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="626" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="627" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="628" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="629" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="630" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="631" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="632" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="633" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="634" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="635" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="636" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="637" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="638" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="639" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="640" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="641" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="642" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="643" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="644" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="645" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="646" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="647" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="648" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="649" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="650" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="651" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="652" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="653" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="654" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="655" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="656" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="657" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="658" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="659" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="660" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="661" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="662" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="663" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="664" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="665" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="666" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="667" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="668" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="669" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="670" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="671" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="672" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="673" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="674" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="675" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="676" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="677" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="678" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="679" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="680" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="681" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="682" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="683" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="684" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="685" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="686" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="687" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="688" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="689" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="690" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="691" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="692" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="693" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="694" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="695" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="696" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="697" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="698" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="699" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="700" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="701" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="702" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="703" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="704" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="705" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="706" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="707" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="708" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="709" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="710" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="711" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="712" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="713" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="714" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="715" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="716" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="717" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="718" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="719" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="720" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="721" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="722" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="723" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="724" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="725" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="726" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="727" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="728" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="729" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="730" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="731" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="732" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="733" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="734" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="735" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="736" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="737" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="738" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="739" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="740" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="741" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="742" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="743" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="744" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="745" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="746" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="747" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="748" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="749" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="750" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="751" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="752" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="753" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="754" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="755" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="756" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="757" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="758" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="759" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="760" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="761" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="762" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="763" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="764" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="765" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="766" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="767" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="768" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="769" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="770" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="771" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="772" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="773" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="774" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="775" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="776" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="777" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="778" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="779" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="780" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="781" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="782" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="783" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="784" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="785" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="786" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="787" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="788" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="789" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="790" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="791" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="792" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="793" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="794" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="795" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="796" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="797" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="798" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="799" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="800" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="801" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="802" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="803" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="804" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="805" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="806" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="807" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="808" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="809" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="810" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="811" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="812" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="813" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="814" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="815" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="816" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="817" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="818" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="819" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="820" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="821" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="822" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="823" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="824" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="825" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="826" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="827" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="828" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="829" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="830" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="831" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="832" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="833" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="834" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="835" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="836" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="837" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="838" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="839" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="840" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="841" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="842" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="843" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="844" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="845" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="846" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="847" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="848" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="849" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="850" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="851" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="852" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="853" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="854" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="855" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="856" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="857" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="858" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="859" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="860" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="861" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="862" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="863" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="864" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="865" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="866" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="867" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="868" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="869" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="870" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="871" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="872" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="873" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="874" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="875" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="876" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="877" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="878" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="879" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="880" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="881" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="882" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="883" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="884" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="885" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="886" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="887" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="888" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="889" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="890" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="891" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="892" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="893" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="894" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="895" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="896" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="897" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="898" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="899" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="900" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="901" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="902" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="903" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="904" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="905" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="906" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="907" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="908" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="909" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="910" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="911" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="912" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="913" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="914" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="915" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="916" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="917" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="918" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="919" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="920" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="921" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="922" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="923" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="924" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="925" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="926" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="927" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="928" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="929" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="930" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="931" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="932" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="933" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="934" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="935" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="936" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="937" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="938" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="939" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="940" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="941" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="942" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="943" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="944" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="945" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="946" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="947" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="948" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="949" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="950" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="951" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="952" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="953" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="954" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="955" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="956" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="957" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="958" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="959" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="960" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="961" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="962" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="963" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="964" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="965" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="966" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="967" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="968" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="969" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="970" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="971" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="972" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="973" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="974" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="975" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="976" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="977" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="978" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="979" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="980" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="981" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="982" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="983" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="984" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="985" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="986" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="987" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="988" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="989" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="990" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="991" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="992" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="993" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="994" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="995" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="996" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="997" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="998" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="999" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="1000" customFormat="1" ht="12.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="31">
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
@@ -9956,142 +11478,142 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="79" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="79" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1" s="67"/>
+      <c r="S1" s="79" t="s">
+        <v>7</v>
+      </c>
+      <c r="T1" s="52"/>
+    </row>
+    <row r="2" spans="1:26" ht="18" customHeight="1">
+      <c r="A2" s="61"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="80"/>
+      <c r="P2" s="81"/>
+      <c r="Q2" s="80"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="93"/>
+    </row>
+    <row r="3" spans="1:26" ht="18" customHeight="1">
+      <c r="A3" s="61"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="82"/>
+      <c r="T3" s="94"/>
+    </row>
+    <row r="4" spans="1:26" ht="18" customHeight="1">
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="83"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="83"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="83"/>
+      <c r="R4" s="65"/>
+      <c r="S4" s="83"/>
+      <c r="T4" s="104"/>
+    </row>
+    <row r="5" spans="1:26" ht="18" customHeight="1">
+      <c r="A5" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="64" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="64" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="64" t="s">
-        <v>6</v>
-      </c>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="64" t="s">
-        <v>7</v>
-      </c>
-      <c r="R1" s="50"/>
-      <c r="S1" s="64" t="s">
-        <v>8</v>
-      </c>
-      <c r="T1" s="52"/>
-    </row>
-    <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="57"/>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="66"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="66"/>
-      <c r="S2" s="65"/>
-      <c r="T2" s="56"/>
-    </row>
-    <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="57"/>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="58"/>
-      <c r="M3" s="58"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="67"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="67"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="67"/>
-      <c r="T3" s="59"/>
-    </row>
-    <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="81"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
-      <c r="N4" s="81"/>
-      <c r="O4" s="80"/>
-      <c r="P4" s="81"/>
-      <c r="Q4" s="80"/>
-      <c r="R4" s="81"/>
-      <c r="S4" s="80"/>
-      <c r="T4" s="100"/>
-    </row>
-    <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="48" t="s">
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="94" t="s">
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="51"/>
+      <c r="N5" s="51"/>
+      <c r="O5" s="51"/>
+      <c r="P5" s="51"/>
+      <c r="Q5" s="51"/>
+      <c r="R5" s="51"/>
+      <c r="S5" s="51"/>
+      <c r="T5" s="52"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="89" t="s">
         <v>34</v>
-      </c>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="49"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="52"/>
-    </row>
-    <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="53" t="s">
-        <v>35</v>
       </c>
       <c r="B6" s="40"/>
       <c r="C6" s="40"/>
       <c r="D6" s="40"/>
       <c r="E6" s="40"/>
       <c r="F6" s="41"/>
-      <c r="G6" s="42" t="s">
-        <v>19</v>
+      <c r="G6" s="53" t="s">
+        <v>18</v>
       </c>
       <c r="H6" s="40"/>
       <c r="I6" s="40"/>
@@ -10105,19 +11627,19 @@
       <c r="Q6" s="40"/>
       <c r="R6" s="40"/>
       <c r="S6" s="40"/>
-      <c r="T6" s="43"/>
+      <c r="T6" s="54"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="53" t="s">
-        <v>36</v>
+      <c r="A7" s="89" t="s">
+        <v>35</v>
       </c>
       <c r="B7" s="40"/>
       <c r="C7" s="40"/>
       <c r="D7" s="40"/>
       <c r="E7" s="40"/>
       <c r="F7" s="41"/>
-      <c r="G7" s="42" t="s">
-        <v>37</v>
+      <c r="G7" s="53" t="s">
+        <v>36</v>
       </c>
       <c r="H7" s="40"/>
       <c r="I7" s="40"/>
@@ -10131,7 +11653,7 @@
       <c r="Q7" s="40"/>
       <c r="R7" s="40"/>
       <c r="S7" s="40"/>
-      <c r="T7" s="43"/>
+      <c r="T7" s="54"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -10159,11 +11681,11 @@
       <c r="A9" s="21"/>
       <c r="B9" s="22"/>
       <c r="C9" s="23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F9" s="24"/>
       <c r="G9" s="25"/>
@@ -10193,7 +11715,7 @@
       <c r="C10" s="27"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F10" s="22"/>
       <c r="G10" s="28"/>
@@ -10223,7 +11745,7 @@
       <c r="C11" s="27"/>
       <c r="D11" s="22"/>
       <c r="E11" s="22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11" s="22"/>
       <c r="G11" s="28"/>
@@ -10253,7 +11775,7 @@
       <c r="C12" s="27"/>
       <c r="D12" s="22"/>
       <c r="E12" s="22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F12" s="22"/>
       <c r="G12" s="28"/>
@@ -10283,7 +11805,7 @@
       <c r="C13" s="29"/>
       <c r="D13" s="30"/>
       <c r="E13" s="30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F13" s="30"/>
       <c r="G13" s="31"/>
@@ -10330,76 +11852,76 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="53" t="s">
-        <v>44</v>
+      <c r="A15" s="89" t="s">
+        <v>43</v>
       </c>
       <c r="B15" s="41"/>
       <c r="C15" s="103" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" s="41"/>
-      <c r="E15" s="69" t="s">
+      <c r="E15" s="95" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="41"/>
+      <c r="G15" s="95" t="s">
         <v>45</v>
-      </c>
-      <c r="F15" s="41"/>
-      <c r="G15" s="69" t="s">
-        <v>46</v>
       </c>
       <c r="H15" s="40"/>
       <c r="I15" s="41"/>
-      <c r="J15" s="69" t="s">
+      <c r="J15" s="95" t="s">
+        <v>46</v>
+      </c>
+      <c r="K15" s="41"/>
+      <c r="L15" s="95" t="s">
         <v>47</v>
-      </c>
-      <c r="K15" s="41"/>
-      <c r="L15" s="69" t="s">
-        <v>48</v>
       </c>
       <c r="M15" s="40"/>
       <c r="N15" s="41"/>
-      <c r="O15" s="69" t="s">
-        <v>49</v>
+      <c r="O15" s="95" t="s">
+        <v>48</v>
       </c>
       <c r="P15" s="40"/>
       <c r="Q15" s="41"/>
       <c r="R15" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="S15" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="S15" s="15" t="s">
+      <c r="T15" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="T15" s="32" t="s">
+    </row>
+    <row r="16" spans="1:26" ht="48" customHeight="1">
+      <c r="A16" s="96">
+        <v>1</v>
+      </c>
+      <c r="B16" s="41"/>
+      <c r="C16" s="97" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="101">
-        <v>1</v>
-      </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="102" t="s">
+      <c r="D16" s="41"/>
+      <c r="E16" s="97" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="41"/>
-      <c r="E16" s="102" t="s">
+      <c r="F16" s="41"/>
+      <c r="G16" s="102" t="s">
         <v>54</v>
-      </c>
-      <c r="F16" s="41"/>
-      <c r="G16" s="96" t="s">
-        <v>55</v>
       </c>
       <c r="H16" s="40"/>
       <c r="I16" s="41"/>
-      <c r="J16" s="96" t="s">
+      <c r="J16" s="102" t="s">
+        <v>55</v>
+      </c>
+      <c r="K16" s="41"/>
+      <c r="L16" s="100" t="s">
         <v>56</v>
-      </c>
-      <c r="K16" s="41"/>
-      <c r="L16" s="98" t="s">
-        <v>57</v>
       </c>
       <c r="M16" s="40"/>
       <c r="N16" s="41"/>
-      <c r="O16" s="98" t="s">
-        <v>58</v>
+      <c r="O16" s="100" t="s">
+        <v>57</v>
       </c>
       <c r="P16" s="40"/>
       <c r="Q16" s="41"/>
@@ -10414,34 +11936,34 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="101">
+      <c r="A17" s="96">
         <v>2</v>
       </c>
       <c r="B17" s="41"/>
-      <c r="C17" s="102" t="s">
+      <c r="C17" s="97" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="41"/>
+      <c r="E17" s="97" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="41"/>
-      <c r="E17" s="102" t="s">
+      <c r="F17" s="41"/>
+      <c r="G17" s="102" t="s">
         <v>60</v>
-      </c>
-      <c r="F17" s="41"/>
-      <c r="G17" s="96" t="s">
-        <v>61</v>
       </c>
       <c r="H17" s="40"/>
       <c r="I17" s="41"/>
-      <c r="J17" s="96" t="s">
+      <c r="J17" s="102" t="s">
+        <v>61</v>
+      </c>
+      <c r="K17" s="41"/>
+      <c r="L17" s="100" t="s">
         <v>62</v>
-      </c>
-      <c r="K17" s="41"/>
-      <c r="L17" s="98" t="s">
-        <v>63</v>
       </c>
       <c r="M17" s="40"/>
       <c r="N17" s="41"/>
-      <c r="O17" s="98" t="s">
-        <v>64</v>
+      <c r="O17" s="100" t="s">
+        <v>63</v>
       </c>
       <c r="P17" s="40"/>
       <c r="Q17" s="41"/>
@@ -10456,21 +11978,21 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="101"/>
+      <c r="A18" s="96"/>
       <c r="B18" s="41"/>
-      <c r="C18" s="102"/>
+      <c r="C18" s="97"/>
       <c r="D18" s="41"/>
-      <c r="E18" s="102"/>
+      <c r="E18" s="97"/>
       <c r="F18" s="41"/>
-      <c r="G18" s="96"/>
+      <c r="G18" s="102"/>
       <c r="H18" s="40"/>
       <c r="I18" s="41"/>
-      <c r="J18" s="96"/>
+      <c r="J18" s="102"/>
       <c r="K18" s="41"/>
-      <c r="L18" s="98"/>
+      <c r="L18" s="100"/>
       <c r="M18" s="40"/>
       <c r="N18" s="41"/>
-      <c r="O18" s="98"/>
+      <c r="O18" s="100"/>
       <c r="P18" s="40"/>
       <c r="Q18" s="41"/>
       <c r="R18" s="33"/>
@@ -10484,21 +12006,21 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="101"/>
+      <c r="A19" s="96"/>
       <c r="B19" s="41"/>
-      <c r="C19" s="102"/>
+      <c r="C19" s="97"/>
       <c r="D19" s="41"/>
-      <c r="E19" s="102"/>
+      <c r="E19" s="97"/>
       <c r="F19" s="41"/>
-      <c r="G19" s="96"/>
+      <c r="G19" s="102"/>
       <c r="H19" s="40"/>
       <c r="I19" s="41"/>
-      <c r="J19" s="96"/>
+      <c r="J19" s="102"/>
       <c r="K19" s="41"/>
-      <c r="L19" s="98"/>
+      <c r="L19" s="100"/>
       <c r="M19" s="40"/>
       <c r="N19" s="41"/>
-      <c r="O19" s="98"/>
+      <c r="O19" s="100"/>
       <c r="P19" s="40"/>
       <c r="Q19" s="41"/>
       <c r="R19" s="33"/>
@@ -10512,21 +12034,21 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="101"/>
+      <c r="A20" s="96"/>
       <c r="B20" s="41"/>
-      <c r="C20" s="102"/>
+      <c r="C20" s="97"/>
       <c r="D20" s="41"/>
-      <c r="E20" s="102"/>
+      <c r="E20" s="97"/>
       <c r="F20" s="41"/>
-      <c r="G20" s="96"/>
+      <c r="G20" s="102"/>
       <c r="H20" s="40"/>
       <c r="I20" s="41"/>
-      <c r="J20" s="96"/>
+      <c r="J20" s="102"/>
       <c r="K20" s="41"/>
-      <c r="L20" s="98"/>
+      <c r="L20" s="100"/>
       <c r="M20" s="40"/>
       <c r="N20" s="41"/>
-      <c r="O20" s="98"/>
+      <c r="O20" s="100"/>
       <c r="P20" s="40"/>
       <c r="Q20" s="41"/>
       <c r="R20" s="33"/>
@@ -10540,21 +12062,21 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="101"/>
+      <c r="A21" s="96"/>
       <c r="B21" s="41"/>
-      <c r="C21" s="102"/>
+      <c r="C21" s="97"/>
       <c r="D21" s="41"/>
-      <c r="E21" s="102"/>
+      <c r="E21" s="97"/>
       <c r="F21" s="41"/>
-      <c r="G21" s="96"/>
+      <c r="G21" s="102"/>
       <c r="H21" s="40"/>
       <c r="I21" s="41"/>
-      <c r="J21" s="96"/>
+      <c r="J21" s="102"/>
       <c r="K21" s="41"/>
-      <c r="L21" s="98"/>
+      <c r="L21" s="100"/>
       <c r="M21" s="40"/>
       <c r="N21" s="41"/>
-      <c r="O21" s="98"/>
+      <c r="O21" s="100"/>
       <c r="P21" s="40"/>
       <c r="Q21" s="41"/>
       <c r="R21" s="33"/>
@@ -10568,21 +12090,21 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="101"/>
+      <c r="A22" s="96"/>
       <c r="B22" s="41"/>
-      <c r="C22" s="102"/>
+      <c r="C22" s="97"/>
       <c r="D22" s="41"/>
-      <c r="E22" s="102"/>
+      <c r="E22" s="97"/>
       <c r="F22" s="41"/>
-      <c r="G22" s="96"/>
+      <c r="G22" s="102"/>
       <c r="H22" s="40"/>
       <c r="I22" s="41"/>
-      <c r="J22" s="96"/>
+      <c r="J22" s="102"/>
       <c r="K22" s="41"/>
-      <c r="L22" s="98"/>
+      <c r="L22" s="100"/>
       <c r="M22" s="40"/>
       <c r="N22" s="41"/>
-      <c r="O22" s="98"/>
+      <c r="O22" s="100"/>
       <c r="P22" s="40"/>
       <c r="Q22" s="41"/>
       <c r="R22" s="33"/>
@@ -10596,21 +12118,21 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="101"/>
+      <c r="A23" s="96"/>
       <c r="B23" s="41"/>
-      <c r="C23" s="102"/>
+      <c r="C23" s="97"/>
       <c r="D23" s="41"/>
-      <c r="E23" s="102"/>
+      <c r="E23" s="97"/>
       <c r="F23" s="41"/>
-      <c r="G23" s="96"/>
+      <c r="G23" s="102"/>
       <c r="H23" s="40"/>
       <c r="I23" s="41"/>
-      <c r="J23" s="96"/>
+      <c r="J23" s="102"/>
       <c r="K23" s="41"/>
-      <c r="L23" s="98"/>
+      <c r="L23" s="100"/>
       <c r="M23" s="40"/>
       <c r="N23" s="41"/>
-      <c r="O23" s="98"/>
+      <c r="O23" s="100"/>
       <c r="P23" s="40"/>
       <c r="Q23" s="41"/>
       <c r="R23" s="33"/>
@@ -10624,21 +12146,21 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="101"/>
+      <c r="A24" s="96"/>
       <c r="B24" s="41"/>
-      <c r="C24" s="102"/>
+      <c r="C24" s="97"/>
       <c r="D24" s="41"/>
-      <c r="E24" s="102"/>
+      <c r="E24" s="97"/>
       <c r="F24" s="41"/>
-      <c r="G24" s="96"/>
+      <c r="G24" s="102"/>
       <c r="H24" s="40"/>
       <c r="I24" s="41"/>
-      <c r="J24" s="96"/>
+      <c r="J24" s="102"/>
       <c r="K24" s="41"/>
-      <c r="L24" s="98"/>
+      <c r="L24" s="100"/>
       <c r="M24" s="40"/>
       <c r="N24" s="41"/>
-      <c r="O24" s="98"/>
+      <c r="O24" s="100"/>
       <c r="P24" s="40"/>
       <c r="Q24" s="41"/>
       <c r="R24" s="33"/>
@@ -10652,21 +12174,21 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="101"/>
+      <c r="A25" s="96"/>
       <c r="B25" s="41"/>
-      <c r="C25" s="102"/>
+      <c r="C25" s="97"/>
       <c r="D25" s="41"/>
-      <c r="E25" s="102"/>
+      <c r="E25" s="97"/>
       <c r="F25" s="41"/>
-      <c r="G25" s="96"/>
+      <c r="G25" s="102"/>
       <c r="H25" s="40"/>
       <c r="I25" s="41"/>
-      <c r="J25" s="96"/>
+      <c r="J25" s="102"/>
       <c r="K25" s="41"/>
-      <c r="L25" s="98"/>
+      <c r="L25" s="100"/>
       <c r="M25" s="40"/>
       <c r="N25" s="41"/>
-      <c r="O25" s="98"/>
+      <c r="O25" s="100"/>
       <c r="P25" s="40"/>
       <c r="Q25" s="41"/>
       <c r="R25" s="33"/>
@@ -10680,21 +12202,21 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="101"/>
+      <c r="A26" s="96"/>
       <c r="B26" s="41"/>
-      <c r="C26" s="102"/>
+      <c r="C26" s="97"/>
       <c r="D26" s="41"/>
-      <c r="E26" s="102"/>
+      <c r="E26" s="97"/>
       <c r="F26" s="41"/>
-      <c r="G26" s="96"/>
+      <c r="G26" s="102"/>
       <c r="H26" s="40"/>
       <c r="I26" s="41"/>
-      <c r="J26" s="96"/>
+      <c r="J26" s="102"/>
       <c r="K26" s="41"/>
-      <c r="L26" s="98"/>
+      <c r="L26" s="100"/>
       <c r="M26" s="40"/>
       <c r="N26" s="41"/>
-      <c r="O26" s="98"/>
+      <c r="O26" s="100"/>
       <c r="P26" s="40"/>
       <c r="Q26" s="41"/>
       <c r="R26" s="33"/>
@@ -10708,21 +12230,21 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="101"/>
+      <c r="A27" s="96"/>
       <c r="B27" s="41"/>
-      <c r="C27" s="102"/>
+      <c r="C27" s="97"/>
       <c r="D27" s="41"/>
-      <c r="E27" s="102"/>
+      <c r="E27" s="97"/>
       <c r="F27" s="41"/>
-      <c r="G27" s="96"/>
+      <c r="G27" s="102"/>
       <c r="H27" s="40"/>
       <c r="I27" s="41"/>
-      <c r="J27" s="96"/>
+      <c r="J27" s="102"/>
       <c r="K27" s="41"/>
-      <c r="L27" s="98"/>
+      <c r="L27" s="100"/>
       <c r="M27" s="40"/>
       <c r="N27" s="41"/>
-      <c r="O27" s="98"/>
+      <c r="O27" s="100"/>
       <c r="P27" s="40"/>
       <c r="Q27" s="41"/>
       <c r="R27" s="33"/>
@@ -10736,21 +12258,21 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="101"/>
+      <c r="A28" s="96"/>
       <c r="B28" s="41"/>
-      <c r="C28" s="102"/>
+      <c r="C28" s="97"/>
       <c r="D28" s="41"/>
-      <c r="E28" s="102"/>
+      <c r="E28" s="97"/>
       <c r="F28" s="41"/>
-      <c r="G28" s="96"/>
+      <c r="G28" s="102"/>
       <c r="H28" s="40"/>
       <c r="I28" s="41"/>
-      <c r="J28" s="96"/>
+      <c r="J28" s="102"/>
       <c r="K28" s="41"/>
-      <c r="L28" s="98"/>
+      <c r="L28" s="100"/>
       <c r="M28" s="40"/>
       <c r="N28" s="41"/>
-      <c r="O28" s="98"/>
+      <c r="O28" s="100"/>
       <c r="P28" s="40"/>
       <c r="Q28" s="41"/>
       <c r="R28" s="33"/>
@@ -10764,21 +12286,21 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="101"/>
+      <c r="A29" s="96"/>
       <c r="B29" s="41"/>
-      <c r="C29" s="102"/>
+      <c r="C29" s="97"/>
       <c r="D29" s="41"/>
-      <c r="E29" s="102"/>
+      <c r="E29" s="97"/>
       <c r="F29" s="41"/>
-      <c r="G29" s="96"/>
+      <c r="G29" s="102"/>
       <c r="H29" s="40"/>
       <c r="I29" s="41"/>
-      <c r="J29" s="96"/>
+      <c r="J29" s="102"/>
       <c r="K29" s="41"/>
-      <c r="L29" s="98"/>
+      <c r="L29" s="100"/>
       <c r="M29" s="40"/>
       <c r="N29" s="41"/>
-      <c r="O29" s="98"/>
+      <c r="O29" s="100"/>
       <c r="P29" s="40"/>
       <c r="Q29" s="41"/>
       <c r="R29" s="33"/>
@@ -10792,21 +12314,21 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="101"/>
+      <c r="A30" s="96"/>
       <c r="B30" s="41"/>
-      <c r="C30" s="102"/>
+      <c r="C30" s="97"/>
       <c r="D30" s="41"/>
-      <c r="E30" s="102"/>
+      <c r="E30" s="97"/>
       <c r="F30" s="41"/>
-      <c r="G30" s="96"/>
+      <c r="G30" s="102"/>
       <c r="H30" s="40"/>
       <c r="I30" s="41"/>
-      <c r="J30" s="96"/>
+      <c r="J30" s="102"/>
       <c r="K30" s="41"/>
-      <c r="L30" s="98"/>
+      <c r="L30" s="100"/>
       <c r="M30" s="40"/>
       <c r="N30" s="41"/>
-      <c r="O30" s="98"/>
+      <c r="O30" s="100"/>
       <c r="P30" s="40"/>
       <c r="Q30" s="41"/>
       <c r="R30" s="33"/>
@@ -10820,23 +12342,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="104"/>
-      <c r="B31" s="72"/>
-      <c r="C31" s="105"/>
-      <c r="D31" s="72"/>
-      <c r="E31" s="105"/>
-      <c r="F31" s="72"/>
-      <c r="G31" s="97"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="72"/>
-      <c r="J31" s="97"/>
-      <c r="K31" s="72"/>
-      <c r="L31" s="99"/>
-      <c r="M31" s="71"/>
-      <c r="N31" s="72"/>
-      <c r="O31" s="99"/>
-      <c r="P31" s="71"/>
-      <c r="Q31" s="72"/>
+      <c r="A31" s="98"/>
+      <c r="B31" s="57"/>
+      <c r="C31" s="99"/>
+      <c r="D31" s="57"/>
+      <c r="E31" s="99"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="105"/>
+      <c r="H31" s="48"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="105"/>
+      <c r="K31" s="57"/>
+      <c r="L31" s="101"/>
+      <c r="M31" s="48"/>
+      <c r="N31" s="57"/>
+      <c r="O31" s="101"/>
+      <c r="P31" s="48"/>
+      <c r="Q31" s="57"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -11834,6 +13356,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -11858,118 +13492,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_コメント投稿機能.xlsx
+++ b/document/成果物ドキュメント_コメント投稿機能.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER124\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828B4931-553A-45E1-9D80-4A6B9409509C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{516FC6E4-2943-4C55-80A0-162E90EED2A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="10905" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="96">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -296,10 +296,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>comment-add-servlet</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>comment-post-form.jsp</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -307,13 +303,6 @@
     <t>チーム名 62期</t>
     <rPh sb="7" eb="8">
       <t>キ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>投稿コメント</t>
-    <rPh sb="0" eb="2">
-      <t>トウコウ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -435,26 +424,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>投稿する</t>
-    <rPh sb="0" eb="2">
-      <t>トウコウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>入力必須、最大100文字</t>
-    <rPh sb="0" eb="4">
-      <t>ニュウリョクヒッス</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>サイダイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>モジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>コメント投稿完了画面</t>
     <rPh sb="4" eb="6">
       <t>トウコウ</t>
@@ -469,13 +438,6 @@
   </si>
   <si>
     <t>メニュー画面へ</t>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>メニュー画面へ</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -484,17 +446,22 @@
   </si>
   <si>
     <t>コメント投稿画面へ</t>
-    <rPh sb="4" eb="8">
-      <t>トウコウガメン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>コメント投稿画面へ</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>GET</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>comment-post-servlet</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>投稿コメント</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>入力必須、最大100文字</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1256,7 +1223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1398,23 +1365,59 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1422,11 +1425,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1443,26 +1446,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -1473,49 +1467,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1525,6 +1492,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1545,11 +1515,29 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1557,25 +1545,16 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1599,23 +1578,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>212911</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>-1</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>142165</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>142164</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1023901</xdr:colOff>
+      <xdr:colOff>707477</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>89647</xdr:rowOff>
+      <xdr:rowOff>99308</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5573D14A-743D-2BA4-3F02-17B67ADDC74C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BE72F39-0E42-9CB6-9B6C-6E9C1E46044B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1638,8 +1617,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="212911" y="896470"/>
-          <a:ext cx="8509431" cy="3070412"/>
+          <a:off x="483359" y="1677537"/>
+          <a:ext cx="7900984" cy="2302853"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1666,22 +1645,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>312965</xdr:colOff>
+      <xdr:colOff>231321</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>27212</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>163286</xdr:colOff>
+      <xdr:colOff>129975</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>20712</xdr:rowOff>
+      <xdr:rowOff>54427</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5328A1BE-8E67-2342-8335-403D27FB135F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{951DCFA7-56D2-533E-C1FD-FD591AFD6481}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1704,8 +1683,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="993322" y="925286"/>
-          <a:ext cx="6885214" cy="4592712"/>
+          <a:off x="911678" y="952498"/>
+          <a:ext cx="6933547" cy="4599215"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2251,7 +2230,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="41"/>
-      <c r="I13" s="106">
+      <c r="I13" s="47">
         <v>46129</v>
       </c>
       <c r="J13" s="40"/>
@@ -2279,7 +2258,7 @@
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
       <c r="G17" s="42" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H17" s="43"/>
       <c r="I17" s="43"/>
@@ -3298,19 +3277,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="79" t="s">
+      <c r="B1" s="71"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="67"/>
-      <c r="F1" s="79" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="67"/>
+      <c r="G1" s="49"/>
       <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
@@ -3322,88 +3301,88 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="61"/>
+      <c r="A2" s="73"/>
       <c r="B2" s="43"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="80" t="s">
+      <c r="C2" s="53"/>
+      <c r="D2" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="80" t="s">
+      <c r="E2" s="51"/>
+      <c r="F2" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="84">
+      <c r="G2" s="51"/>
+      <c r="H2" s="56">
         <v>46122</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="60"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="61"/>
+      <c r="A3" s="73"/>
       <c r="B3" s="43"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="61"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="78"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="62"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="66" t="s">
+      <c r="A5" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="50" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="52"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="83" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="84"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="68" t="s">
+      <c r="A6" s="64" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="40"/>
       <c r="C6" s="41"/>
-      <c r="D6" s="53" t="s">
-        <v>83</v>
+      <c r="D6" s="65" t="s">
+        <v>81</v>
       </c>
       <c r="E6" s="40"/>
       <c r="F6" s="40"/>
       <c r="G6" s="40"/>
       <c r="H6" s="40"/>
       <c r="I6" s="40"/>
-      <c r="J6" s="54"/>
+      <c r="J6" s="66"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="68" t="s">
+      <c r="A7" s="64" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="40"/>
       <c r="C7" s="41"/>
-      <c r="D7" s="53" t="s">
+      <c r="D7" s="65" t="s">
         <v>68</v>
       </c>
       <c r="E7" s="40"/>
@@ -3411,15 +3390,15 @@
       <c r="G7" s="40"/>
       <c r="H7" s="40"/>
       <c r="I7" s="40"/>
-      <c r="J7" s="54"/>
+      <c r="J7" s="66"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="68" t="s">
+      <c r="A8" s="64" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="40"/>
       <c r="C8" s="41"/>
-      <c r="D8" s="53" t="s">
+      <c r="D8" s="65" t="s">
         <v>69</v>
       </c>
       <c r="E8" s="40"/>
@@ -3427,87 +3406,87 @@
       <c r="G8" s="40"/>
       <c r="H8" s="40"/>
       <c r="I8" s="40"/>
-      <c r="J8" s="54"/>
+      <c r="J8" s="66"/>
     </row>
     <row r="9" spans="1:10" ht="87.75" customHeight="1">
-      <c r="A9" s="69" t="s">
+      <c r="A9" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="63" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="41"/>
-      <c r="D9" s="55" t="s">
-        <v>84</v>
+      <c r="D9" s="85" t="s">
+        <v>82</v>
       </c>
       <c r="E9" s="40"/>
       <c r="F9" s="40"/>
       <c r="G9" s="40"/>
       <c r="H9" s="40"/>
       <c r="I9" s="40"/>
-      <c r="J9" s="54"/>
+      <c r="J9" s="66"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="70"/>
-      <c r="B10" s="72" t="s">
+      <c r="A10" s="79"/>
+      <c r="B10" s="63" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="41"/>
-      <c r="D10" s="55" t="s">
-        <v>85</v>
+      <c r="D10" s="85" t="s">
+        <v>83</v>
       </c>
       <c r="E10" s="40"/>
       <c r="F10" s="40"/>
       <c r="G10" s="40"/>
       <c r="H10" s="40"/>
       <c r="I10" s="40"/>
-      <c r="J10" s="54"/>
+      <c r="J10" s="66"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="71"/>
-      <c r="B11" s="72" t="s">
+      <c r="A11" s="80"/>
+      <c r="B11" s="63" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="41"/>
-      <c r="D11" s="55" t="s">
-        <v>86</v>
+      <c r="D11" s="85" t="s">
+        <v>84</v>
       </c>
       <c r="E11" s="40"/>
       <c r="F11" s="40"/>
       <c r="G11" s="40"/>
       <c r="H11" s="40"/>
       <c r="I11" s="40"/>
-      <c r="J11" s="54"/>
+      <c r="J11" s="66"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="68" t="s">
+      <c r="A12" s="64" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="40"/>
       <c r="C12" s="41"/>
-      <c r="D12" s="53" t="s">
-        <v>87</v>
+      <c r="D12" s="65" t="s">
+        <v>85</v>
       </c>
       <c r="E12" s="40"/>
       <c r="F12" s="40"/>
       <c r="G12" s="40"/>
       <c r="H12" s="40"/>
       <c r="I12" s="40"/>
-      <c r="J12" s="54"/>
+      <c r="J12" s="66"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="56" t="s">
+      <c r="A13" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="48"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="49"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="81"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="82"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4498,17 +4477,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -4517,14 +4493,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4543,19 +4522,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="79" t="s">
+      <c r="B1" s="71"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="67"/>
-      <c r="F1" s="79" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="67"/>
+      <c r="G1" s="49"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -4567,48 +4546,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="61"/>
+      <c r="A2" s="73"/>
       <c r="B2" s="43"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="80" t="s">
+      <c r="C2" s="53"/>
+      <c r="D2" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="80" t="s">
+      <c r="E2" s="51"/>
+      <c r="F2" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="84">
+      <c r="G2" s="51"/>
+      <c r="H2" s="56">
         <v>46120</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="59" t="s">
         <v>66</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="60"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="61"/>
+      <c r="A3" s="73"/>
       <c r="B3" s="43"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="61"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="78"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="62"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -5962,19 +5941,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="79" t="s">
+      <c r="B1" s="71"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="67"/>
-      <c r="F1" s="79" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="67"/>
+      <c r="G1" s="49"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -5986,48 +5965,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="61"/>
+      <c r="A2" s="73"/>
       <c r="B2" s="43"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="80" t="s">
+      <c r="C2" s="53"/>
+      <c r="D2" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="80" t="s">
+      <c r="E2" s="51"/>
+      <c r="F2" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="84">
+      <c r="G2" s="51"/>
+      <c r="H2" s="56">
         <v>46125</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="60"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="61"/>
+      <c r="A3" s="73"/>
       <c r="B3" s="43"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="61"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="78"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="62"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7367,7 +7346,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J1000"/>
+  <dimension ref="A1:J995"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
@@ -7376,19 +7355,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="79" t="s">
+      <c r="B1" s="71"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="67"/>
-      <c r="F1" s="79" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="67"/>
+      <c r="G1" s="49"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -7400,64 +7379,64 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="61"/>
+      <c r="A2" s="73"/>
       <c r="B2" s="43"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="80" t="s">
+      <c r="C2" s="53"/>
+      <c r="D2" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="80" t="s">
+      <c r="E2" s="51"/>
+      <c r="F2" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="84">
+      <c r="G2" s="51"/>
+      <c r="H2" s="56">
         <v>46122</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="60"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="61"/>
+      <c r="A3" s="73"/>
       <c r="B3" s="43"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="61"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="61"/>
+      <c r="A4" s="73"/>
       <c r="B4" s="43"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="61"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
       <c r="A5" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="90" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="52"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="91" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="84"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="89" t="s">
@@ -7471,22 +7450,22 @@
       <c r="G6" s="40"/>
       <c r="H6" s="40"/>
       <c r="I6" s="40"/>
-      <c r="J6" s="54"/>
+      <c r="J6" s="66"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="91"/>
-      <c r="B7" s="92"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="93"/>
+      <c r="A7" s="92"/>
+      <c r="B7" s="93"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="93"/>
+      <c r="E7" s="93"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="93"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="94"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="61"/>
+      <c r="A8" s="73"/>
       <c r="B8" s="43"/>
       <c r="C8" s="43"/>
       <c r="D8" s="43"/>
@@ -7495,10 +7474,10 @@
       <c r="G8" s="43"/>
       <c r="H8" s="43"/>
       <c r="I8" s="43"/>
-      <c r="J8" s="94"/>
+      <c r="J8" s="95"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="61"/>
+      <c r="A9" s="73"/>
       <c r="B9" s="43"/>
       <c r="C9" s="43"/>
       <c r="D9" s="43"/>
@@ -7507,10 +7486,10 @@
       <c r="G9" s="43"/>
       <c r="H9" s="43"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="94"/>
+      <c r="J9" s="95"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="61"/>
+      <c r="A10" s="73"/>
       <c r="B10" s="43"/>
       <c r="C10" s="43"/>
       <c r="D10" s="43"/>
@@ -7519,10 +7498,10 @@
       <c r="G10" s="43"/>
       <c r="H10" s="43"/>
       <c r="I10" s="43"/>
-      <c r="J10" s="94"/>
+      <c r="J10" s="95"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="61"/>
+      <c r="A11" s="73"/>
       <c r="B11" s="43"/>
       <c r="C11" s="43"/>
       <c r="D11" s="43"/>
@@ -7531,10 +7510,10 @@
       <c r="G11" s="43"/>
       <c r="H11" s="43"/>
       <c r="I11" s="43"/>
-      <c r="J11" s="94"/>
+      <c r="J11" s="95"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="61"/>
+      <c r="A12" s="73"/>
       <c r="B12" s="43"/>
       <c r="C12" s="43"/>
       <c r="D12" s="43"/>
@@ -7543,10 +7522,10 @@
       <c r="G12" s="43"/>
       <c r="H12" s="43"/>
       <c r="I12" s="43"/>
-      <c r="J12" s="94"/>
+      <c r="J12" s="95"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="61"/>
+      <c r="A13" s="73"/>
       <c r="B13" s="43"/>
       <c r="C13" s="43"/>
       <c r="D13" s="43"/>
@@ -7555,7 +7534,7 @@
       <c r="G13" s="43"/>
       <c r="H13" s="43"/>
       <c r="I13" s="43"/>
-      <c r="J13" s="94"/>
+      <c r="J13" s="95"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="89" t="s">
@@ -7569,7 +7548,7 @@
       <c r="G14" s="40"/>
       <c r="H14" s="40"/>
       <c r="I14" s="40"/>
-      <c r="J14" s="54"/>
+      <c r="J14" s="66"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="89" t="s">
@@ -7577,8 +7556,8 @@
       </c>
       <c r="B15" s="40"/>
       <c r="C15" s="41"/>
-      <c r="D15" s="53" t="s">
-        <v>78</v>
+      <c r="D15" s="65" t="s">
+        <v>93</v>
       </c>
       <c r="E15" s="40"/>
       <c r="F15" s="40"/>
@@ -7609,20 +7588,20 @@
       <c r="G16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="95" t="s">
+      <c r="H16" s="96" t="s">
         <v>17</v>
       </c>
       <c r="I16" s="40"/>
-      <c r="J16" s="54"/>
+      <c r="J16" s="66"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="86" t="s">
+      <c r="A17" s="90" t="s">
         <v>72</v>
       </c>
       <c r="B17" s="40"/>
       <c r="C17" s="41"/>
       <c r="D17" s="17" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>73</v>
@@ -7631,92 +7610,37 @@
         <v>74</v>
       </c>
       <c r="G17" s="18"/>
-      <c r="H17" s="53" t="s">
-        <v>91</v>
+      <c r="H17" s="65" t="s">
+        <v>95</v>
       </c>
       <c r="I17" s="40"/>
-      <c r="J17" s="54"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="86" t="s">
+      <c r="J17" s="66"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A18" s="88" t="s">
         <v>75</v>
       </c>
-      <c r="B18" s="40"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="E18" s="17" t="s">
+      <c r="B18" s="68"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="H18" s="53"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="54"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="86"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="54"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="86"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="54"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="86"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="54"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="86"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="54"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="88"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="48"/>
-      <c r="J23" s="49"/>
-    </row>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="H18" s="81"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="82"/>
+    </row>
+    <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="23" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7726,987 +7650,978 @@
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="34" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="35" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="36" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="37" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="38" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="39" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="40" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="41" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="42" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="43" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="44" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="45" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="46" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="47" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="48" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="49" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="50" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="51" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="52" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="53" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="54" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="55" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="56" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="57" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="58" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="59" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="60" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="61" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="62" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="63" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="64" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="65" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="66" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="67" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="68" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="69" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="70" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="71" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="72" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="74" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="75" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="76" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="77" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="78" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="79" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="80" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="81" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="82" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="83" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="84" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="85" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="86" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="87" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="88" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="89" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="90" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="91" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="92" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="93" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="94" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="96" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="97" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="98" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="99" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="100" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="101" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="102" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="104" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="105" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="106" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="107" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="108" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="109" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="110" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="111" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="112" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="113" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="114" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="115" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="116" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="117" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="118" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="119" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="120" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="121" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="122" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="123" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="124" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="125" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="126" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="127" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="128" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="129" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="130" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="131" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="132" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="133" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="134" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="135" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="136" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="137" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="139" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="140" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="141" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="142" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="143" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="144" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="145" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="146" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="147" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="148" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="149" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="150" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="151" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="152" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="153" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="154" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="155" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="156" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="157" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="158" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="160" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="161" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="162" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="163" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="164" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="165" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="166" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="167" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="168" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="169" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="170" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="171" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="172" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="173" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="174" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="175" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="176" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="177" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="178" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="179" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="180" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="181" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="182" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="183" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="184" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="185" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="186" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="187" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="188" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="189" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="190" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="191" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="192" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="193" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="194" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="195" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="196" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="197" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="198" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="199" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="200" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="201" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="202" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="203" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="204" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="205" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="206" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="207" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="208" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="209" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="210" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="211" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="212" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="213" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="214" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="215" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="216" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="217" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="218" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="219" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="220" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="221" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="222" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="223" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="224" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="225" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="226" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="227" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="228" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="229" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="230" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="231" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="232" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="233" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="234" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="235" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="236" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="237" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="238" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="239" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="240" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="241" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="242" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="243" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="244" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="245" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="246" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="247" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="248" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="249" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="250" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="251" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="252" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="253" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="254" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="255" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="256" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="257" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="258" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="259" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="260" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="261" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="262" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="263" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="264" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="265" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="266" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="267" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="268" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="269" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="270" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="271" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="272" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="273" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="274" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="275" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="276" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="277" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="278" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="279" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="280" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="281" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="282" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="283" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="284" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="285" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="286" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="287" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="288" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="289" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="290" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="291" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="292" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="293" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="294" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="295" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="296" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="297" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="298" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="299" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="300" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="301" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="302" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="303" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="304" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="305" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="306" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="307" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="308" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="309" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="310" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="311" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="312" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="313" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="314" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="315" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="316" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="317" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="318" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="319" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="320" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="321" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="322" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="323" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="324" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="325" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="326" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="327" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="328" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="329" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="330" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="331" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="332" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="333" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="334" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="335" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="336" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="337" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="338" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="339" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="340" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="341" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="342" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="343" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="344" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="345" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="346" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="347" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="348" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="349" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="350" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="351" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="352" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="353" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="354" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="355" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="356" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="357" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="358" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="359" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="360" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="361" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="362" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="363" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="364" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="365" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="366" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="367" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="368" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="369" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="370" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="371" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="372" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="373" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="374" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="375" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="376" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="377" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="378" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="379" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="380" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="381" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="382" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="383" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="384" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="385" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="386" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="387" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="388" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="389" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="390" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="391" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="392" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="393" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="394" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="395" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="396" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="397" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="398" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="399" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="400" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="401" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="402" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="403" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="404" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="405" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="406" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="407" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="408" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="409" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="410" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="411" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="412" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="413" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="414" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="415" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="416" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="417" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="418" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="419" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="420" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="421" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="422" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="423" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="424" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="425" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="426" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="427" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="428" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="429" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="430" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="431" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="432" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="433" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="434" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="435" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="436" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="437" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="438" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="439" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="440" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="441" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="442" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="443" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="444" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="445" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="446" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="447" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="448" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="449" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="450" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="451" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="452" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="453" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="454" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="455" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="456" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="457" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="458" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="459" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="460" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="461" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="462" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="463" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="464" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="465" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="466" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="467" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="468" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="469" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="470" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="471" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="472" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="473" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="474" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="475" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="476" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="477" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="478" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="479" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="480" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="481" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="482" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="483" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="484" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="485" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="486" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="487" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="488" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="489" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="490" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="491" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="492" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="493" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="494" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="495" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="496" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="497" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="498" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="499" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="500" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="501" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="502" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="503" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="504" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="505" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="506" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="507" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="508" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="509" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="510" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="511" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="512" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="513" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="514" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="515" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="516" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="517" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="518" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="519" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="520" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="521" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="522" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="523" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="524" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="525" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="526" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="527" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="528" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="529" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="530" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="531" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="532" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="533" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="534" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="535" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="536" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="537" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="538" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="539" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="540" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="541" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="542" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="543" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="544" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="545" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="546" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="547" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="548" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="549" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="550" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="551" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="552" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="553" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="554" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="555" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="556" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="557" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="558" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="559" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="560" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="561" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="562" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="563" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="564" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="565" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="566" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="567" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="568" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="569" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="570" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="571" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="572" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="573" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="574" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="575" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="576" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="577" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="578" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="579" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="580" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="581" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="582" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="583" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="584" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="585" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="586" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="587" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="588" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="589" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="590" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="591" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="592" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="593" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="594" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="595" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="596" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="597" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="598" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="599" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="600" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="601" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="602" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="603" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="604" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="605" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="606" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="607" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="608" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="609" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="610" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="611" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="612" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="613" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="614" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="615" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="616" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="617" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="618" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="619" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="620" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="621" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="622" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="623" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="624" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="625" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="626" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="627" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="628" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="629" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="630" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="631" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="632" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="633" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="634" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="635" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="636" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="637" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="638" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="639" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="640" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="641" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="642" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="643" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="644" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="645" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="646" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="647" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="648" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="649" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="650" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="651" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="652" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="653" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="654" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="655" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="656" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="657" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="658" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="659" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="660" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="661" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="662" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="663" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="664" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="665" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="666" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="667" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="668" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="669" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="670" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="671" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="672" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="673" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="674" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="675" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="676" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="677" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="678" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="679" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="680" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="681" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="682" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="683" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="684" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="685" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="686" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="687" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="688" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="689" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="690" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="691" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="692" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="693" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="694" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="695" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="696" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="697" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="698" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="699" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="700" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="701" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="702" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="703" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="704" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="705" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="706" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="707" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="708" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="709" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="710" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="711" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="712" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="713" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="714" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="715" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="716" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="717" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="718" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="719" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="720" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="721" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="722" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="723" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="724" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="725" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="726" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="727" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="728" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="729" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="730" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="731" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="732" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="733" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="734" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="735" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="736" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="737" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="738" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="739" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="740" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="741" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="742" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="743" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="744" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="745" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="746" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="747" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="748" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="749" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="750" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="751" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="752" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="753" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="754" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="755" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="756" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="757" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="758" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="759" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="760" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="761" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="762" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="763" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="764" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="765" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="766" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="767" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="768" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="769" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="770" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="771" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="772" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="773" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="774" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="775" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="776" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="777" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="778" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="779" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="780" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="781" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="782" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="783" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="784" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="785" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="786" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="787" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="788" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="789" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="790" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="791" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="792" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="793" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="794" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="795" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="796" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="797" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="798" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="799" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="800" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="801" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="802" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="803" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="804" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="805" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="806" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="807" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="808" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="809" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="810" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="811" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="812" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="813" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="814" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="815" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="816" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="817" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="818" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="819" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="820" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="821" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="822" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="823" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="824" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="825" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="826" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="827" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="828" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="829" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="830" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="831" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="832" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="833" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="834" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="835" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="836" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="837" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="838" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="839" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="840" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="841" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="842" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="843" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="844" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="845" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="846" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="847" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="848" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="849" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="850" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="851" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="852" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="853" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="854" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="855" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="856" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="857" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="858" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="859" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="860" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="861" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="862" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="863" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="864" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="865" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="866" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="867" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="868" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="869" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="870" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="871" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="872" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="873" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="874" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="875" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="876" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="877" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="878" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="879" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="880" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="881" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="882" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="883" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="884" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="885" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="886" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="887" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="888" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="889" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="890" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="891" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="892" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="893" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="894" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="895" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="896" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="897" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="898" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="899" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="900" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="901" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="902" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="903" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="904" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="905" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="906" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="907" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="908" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="909" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="910" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="911" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="912" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="913" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="914" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="915" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="916" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="917" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="918" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="919" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="920" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="921" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="922" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="923" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="924" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="925" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="926" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="927" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="928" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="929" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="930" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="931" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="932" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="933" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="934" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="935" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="936" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="937" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="938" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="939" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="940" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="941" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="942" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="943" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="944" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="945" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="946" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="947" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="948" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="949" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="950" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="951" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="952" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="953" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="954" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="955" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="956" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="957" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="958" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="959" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="960" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="961" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="962" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="963" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="964" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="965" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="966" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="967" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="968" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="969" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="970" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="971" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="972" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="973" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="974" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="975" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="976" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="977" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="978" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="979" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="980" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="981" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="982" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="983" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="984" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="985" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="986" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="987" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="988" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="989" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="990" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="991" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="992" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="993" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="994" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="995" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="996" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="997" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="998" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="999" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1000" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="33" ht="12.75" customHeight="1"/>
+    <row r="34" ht="12.75" customHeight="1"/>
+    <row r="35" ht="12.75" customHeight="1"/>
+    <row r="36" ht="12.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1"/>
+    <row r="38" ht="12.75" customHeight="1"/>
+    <row r="39" ht="12.75" customHeight="1"/>
+    <row r="40" ht="12.75" customHeight="1"/>
+    <row r="41" ht="12.75" customHeight="1"/>
+    <row r="42" ht="12.75" customHeight="1"/>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="47" ht="12.75" customHeight="1"/>
+    <row r="48" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
+    <row r="995" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+  <mergeCells count="21">
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A17:C17"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A7:J13"/>
@@ -8714,19 +8629,13 @@
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="H16:J16"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
     <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8740,7 +8649,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J1000"/>
+  <dimension ref="A1:J994"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
@@ -8752,19 +8661,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="79" t="s">
+      <c r="B1" s="71"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="67"/>
-      <c r="F1" s="79" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="67"/>
+      <c r="G1" s="49"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -8776,64 +8685,64 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="61"/>
+      <c r="A2" s="73"/>
       <c r="B2" s="43"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="80" t="s">
+      <c r="C2" s="53"/>
+      <c r="D2" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="80" t="s">
+      <c r="E2" s="51"/>
+      <c r="F2" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="84">
+      <c r="G2" s="51"/>
+      <c r="H2" s="56">
         <v>46122</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="60"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="61"/>
+      <c r="A3" s="73"/>
       <c r="B3" s="43"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="61"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="61"/>
+      <c r="A4" s="73"/>
       <c r="B4" s="43"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="61"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
       <c r="A5" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="90" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="52"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="91" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="84"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="89" t="s">
@@ -8847,22 +8756,22 @@
       <c r="G6" s="40"/>
       <c r="H6" s="40"/>
       <c r="I6" s="40"/>
-      <c r="J6" s="54"/>
+      <c r="J6" s="66"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="91"/>
-      <c r="B7" s="92"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="93"/>
+      <c r="A7" s="92"/>
+      <c r="B7" s="93"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="93"/>
+      <c r="E7" s="93"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="93"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="94"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="61"/>
+      <c r="A8" s="73"/>
       <c r="B8" s="43"/>
       <c r="C8" s="43"/>
       <c r="D8" s="43"/>
@@ -8871,10 +8780,10 @@
       <c r="G8" s="43"/>
       <c r="H8" s="43"/>
       <c r="I8" s="43"/>
-      <c r="J8" s="94"/>
+      <c r="J8" s="95"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="61"/>
+      <c r="A9" s="73"/>
       <c r="B9" s="43"/>
       <c r="C9" s="43"/>
       <c r="D9" s="43"/>
@@ -8883,10 +8792,10 @@
       <c r="G9" s="43"/>
       <c r="H9" s="43"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="94"/>
+      <c r="J9" s="95"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="61"/>
+      <c r="A10" s="73"/>
       <c r="B10" s="43"/>
       <c r="C10" s="43"/>
       <c r="D10" s="43"/>
@@ -8895,10 +8804,10 @@
       <c r="G10" s="43"/>
       <c r="H10" s="43"/>
       <c r="I10" s="43"/>
-      <c r="J10" s="94"/>
+      <c r="J10" s="95"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="61"/>
+      <c r="A11" s="73"/>
       <c r="B11" s="43"/>
       <c r="C11" s="43"/>
       <c r="D11" s="43"/>
@@ -8907,10 +8816,10 @@
       <c r="G11" s="43"/>
       <c r="H11" s="43"/>
       <c r="I11" s="43"/>
-      <c r="J11" s="94"/>
+      <c r="J11" s="95"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="61"/>
+      <c r="A12" s="73"/>
       <c r="B12" s="43"/>
       <c r="C12" s="43"/>
       <c r="D12" s="43"/>
@@ -8919,10 +8828,10 @@
       <c r="G12" s="43"/>
       <c r="H12" s="43"/>
       <c r="I12" s="43"/>
-      <c r="J12" s="94"/>
+      <c r="J12" s="95"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="61"/>
+      <c r="A13" s="73"/>
       <c r="B13" s="43"/>
       <c r="C13" s="43"/>
       <c r="D13" s="43"/>
@@ -8931,7 +8840,7 @@
       <c r="G13" s="43"/>
       <c r="H13" s="43"/>
       <c r="I13" s="43"/>
-      <c r="J13" s="94"/>
+      <c r="J13" s="95"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="89" t="s">
@@ -8945,7 +8854,7 @@
       <c r="G14" s="40"/>
       <c r="H14" s="40"/>
       <c r="I14" s="40"/>
-      <c r="J14" s="54"/>
+      <c r="J14" s="66"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="89" t="s">
@@ -8953,8 +8862,8 @@
       </c>
       <c r="B15" s="40"/>
       <c r="C15" s="41"/>
-      <c r="D15" s="53" t="s">
-        <v>95</v>
+      <c r="D15" s="65" t="s">
+        <v>90</v>
       </c>
       <c r="E15" s="40"/>
       <c r="F15" s="40"/>
@@ -8964,7 +8873,7 @@
         <v>25</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
@@ -8985,104 +8894,38 @@
       <c r="G16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="95" t="s">
+      <c r="H16" s="96" t="s">
         <v>17</v>
       </c>
       <c r="I16" s="40"/>
-      <c r="J16" s="54"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="86" t="s">
+      <c r="J16" s="66"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A17" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" s="17" t="s">
+      <c r="B17" s="109"/>
+      <c r="C17" s="110"/>
+      <c r="D17" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="H17" s="53"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="54"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="86"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="53"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="54"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="86"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="54"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="86"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="54"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="86"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="54"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="86"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="54"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="88"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="48"/>
-      <c r="J23" s="49"/>
-    </row>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="H17" s="81"/>
+      <c r="I17" s="107"/>
+      <c r="J17" s="108"/>
+    </row>
+    <row r="18" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="23" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9092,995 +8935,970 @@
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="34" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="35" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="36" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="37" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="38" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="39" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="40" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="41" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="42" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="43" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="44" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="45" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="46" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="47" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="48" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="49" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="50" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="51" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="52" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="53" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="54" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="55" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="56" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="57" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="58" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="59" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="60" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="61" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="62" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="63" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="64" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="65" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="66" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="67" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="68" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="69" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="70" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="71" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="72" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="74" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="75" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="76" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="77" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="78" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="79" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="80" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="81" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="82" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="83" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="84" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="85" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="86" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="87" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="88" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="89" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="90" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="91" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="92" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="93" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="94" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="96" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="97" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="98" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="99" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="100" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="101" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="102" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="104" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="105" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="106" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="107" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="108" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="109" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="110" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="111" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="112" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="113" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="114" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="115" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="116" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="117" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="118" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="119" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="120" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="121" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="122" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="123" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="124" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="125" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="126" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="127" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="128" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="129" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="130" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="131" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="132" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="133" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="134" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="135" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="136" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="137" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="139" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="140" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="141" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="142" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="143" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="144" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="145" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="146" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="147" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="148" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="149" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="150" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="151" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="152" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="153" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="154" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="155" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="156" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="157" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="158" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="160" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="161" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="162" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="163" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="164" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="165" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="166" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="167" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="168" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="169" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="170" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="171" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="172" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="173" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="174" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="175" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="176" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="177" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="178" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="179" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="180" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="181" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="182" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="183" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="184" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="185" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="186" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="187" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="188" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="189" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="190" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="191" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="192" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="193" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="194" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="195" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="196" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="197" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="198" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="199" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="200" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="201" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="202" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="203" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="204" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="205" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="206" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="207" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="208" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="209" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="210" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="211" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="212" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="213" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="214" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="215" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="216" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="217" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="218" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="219" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="220" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="221" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="222" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="223" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="224" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="225" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="226" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="227" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="228" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="229" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="230" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="231" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="232" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="233" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="234" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="235" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="236" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="237" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="238" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="239" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="240" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="241" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="242" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="243" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="244" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="245" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="246" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="247" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="248" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="249" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="250" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="251" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="252" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="253" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="254" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="255" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="256" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="257" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="258" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="259" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="260" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="261" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="262" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="263" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="264" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="265" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="266" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="267" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="268" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="269" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="270" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="271" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="272" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="273" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="274" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="275" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="276" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="277" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="278" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="279" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="280" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="281" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="282" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="283" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="284" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="285" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="286" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="287" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="288" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="289" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="290" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="291" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="292" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="293" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="294" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="295" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="296" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="297" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="298" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="299" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="300" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="301" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="302" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="303" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="304" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="305" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="306" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="307" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="308" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="309" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="310" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="311" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="312" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="313" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="314" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="315" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="316" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="317" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="318" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="319" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="320" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="321" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="322" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="323" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="324" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="325" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="326" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="327" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="328" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="329" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="330" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="331" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="332" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="333" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="334" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="335" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="336" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="337" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="338" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="339" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="340" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="341" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="342" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="343" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="344" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="345" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="346" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="347" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="348" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="349" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="350" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="351" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="352" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="353" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="354" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="355" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="356" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="357" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="358" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="359" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="360" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="361" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="362" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="363" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="364" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="365" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="366" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="367" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="368" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="369" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="370" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="371" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="372" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="373" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="374" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="375" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="376" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="377" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="378" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="379" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="380" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="381" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="382" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="383" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="384" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="385" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="386" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="387" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="388" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="389" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="390" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="391" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="392" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="393" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="394" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="395" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="396" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="397" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="398" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="399" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="400" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="401" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="402" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="403" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="404" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="405" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="406" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="407" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="408" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="409" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="410" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="411" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="412" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="413" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="414" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="415" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="416" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="417" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="418" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="419" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="420" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="421" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="422" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="423" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="424" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="425" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="426" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="427" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="428" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="429" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="430" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="431" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="432" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="433" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="434" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="435" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="436" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="437" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="438" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="439" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="440" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="441" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="442" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="443" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="444" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="445" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="446" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="447" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="448" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="449" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="450" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="451" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="452" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="453" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="454" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="455" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="456" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="457" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="458" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="459" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="460" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="461" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="462" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="463" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="464" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="465" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="466" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="467" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="468" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="469" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="470" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="471" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="472" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="473" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="474" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="475" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="476" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="477" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="478" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="479" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="480" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="481" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="482" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="483" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="484" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="485" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="486" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="487" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="488" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="489" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="490" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="491" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="492" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="493" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="494" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="495" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="496" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="497" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="498" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="499" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="500" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="501" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="502" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="503" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="504" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="505" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="506" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="507" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="508" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="509" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="510" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="511" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="512" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="513" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="514" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="515" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="516" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="517" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="518" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="519" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="520" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="521" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="522" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="523" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="524" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="525" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="526" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="527" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="528" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="529" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="530" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="531" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="532" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="533" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="534" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="535" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="536" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="537" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="538" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="539" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="540" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="541" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="542" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="543" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="544" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="545" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="546" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="547" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="548" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="549" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="550" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="551" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="552" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="553" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="554" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="555" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="556" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="557" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="558" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="559" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="560" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="561" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="562" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="563" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="564" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="565" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="566" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="567" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="568" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="569" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="570" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="571" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="572" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="573" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="574" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="575" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="576" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="577" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="578" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="579" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="580" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="581" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="582" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="583" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="584" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="585" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="586" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="587" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="588" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="589" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="590" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="591" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="592" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="593" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="594" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="595" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="596" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="597" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="598" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="599" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="600" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="601" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="602" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="603" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="604" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="605" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="606" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="607" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="608" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="609" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="610" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="611" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="612" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="613" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="614" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="615" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="616" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="617" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="618" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="619" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="620" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="621" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="622" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="623" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="624" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="625" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="626" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="627" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="628" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="629" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="630" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="631" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="632" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="633" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="634" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="635" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="636" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="637" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="638" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="639" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="640" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="641" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="642" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="643" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="644" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="645" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="646" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="647" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="648" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="649" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="650" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="651" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="652" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="653" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="654" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="655" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="656" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="657" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="658" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="659" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="660" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="661" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="662" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="663" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="664" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="665" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="666" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="667" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="668" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="669" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="670" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="671" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="672" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="673" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="674" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="675" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="676" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="677" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="678" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="679" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="680" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="681" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="682" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="683" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="684" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="685" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="686" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="687" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="688" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="689" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="690" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="691" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="692" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="693" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="694" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="695" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="696" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="697" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="698" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="699" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="700" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="701" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="702" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="703" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="704" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="705" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="706" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="707" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="708" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="709" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="710" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="711" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="712" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="713" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="714" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="715" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="716" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="717" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="718" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="719" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="720" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="721" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="722" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="723" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="724" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="725" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="726" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="727" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="728" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="729" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="730" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="731" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="732" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="733" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="734" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="735" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="736" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="737" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="738" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="739" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="740" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="741" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="742" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="743" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="744" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="745" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="746" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="747" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="748" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="749" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="750" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="751" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="752" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="753" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="754" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="755" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="756" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="757" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="758" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="759" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="760" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="761" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="762" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="763" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="764" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="765" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="766" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="767" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="768" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="769" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="770" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="771" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="772" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="773" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="774" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="775" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="776" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="777" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="778" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="779" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="780" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="781" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="782" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="783" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="784" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="785" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="786" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="787" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="788" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="789" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="790" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="791" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="792" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="793" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="794" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="795" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="796" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="797" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="798" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="799" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="800" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="801" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="802" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="803" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="804" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="805" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="806" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="807" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="808" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="809" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="810" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="811" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="812" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="813" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="814" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="815" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="816" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="817" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="818" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="819" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="820" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="821" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="822" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="823" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="824" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="825" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="826" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="827" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="828" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="829" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="830" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="831" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="832" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="833" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="834" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="835" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="836" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="837" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="838" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="839" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="840" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="841" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="842" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="843" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="844" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="845" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="846" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="847" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="848" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="849" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="850" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="851" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="852" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="853" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="854" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="855" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="856" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="857" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="858" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="859" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="860" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="861" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="862" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="863" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="864" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="865" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="866" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="867" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="868" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="869" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="870" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="871" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="872" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="873" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="874" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="875" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="876" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="877" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="878" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="879" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="880" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="881" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="882" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="883" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="884" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="885" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="886" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="887" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="888" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="889" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="890" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="891" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="892" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="893" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="894" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="895" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="896" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="897" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="898" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="899" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="900" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="901" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="902" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="903" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="904" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="905" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="906" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="907" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="908" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="909" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="910" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="911" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="912" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="913" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="914" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="915" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="916" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="917" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="918" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="919" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="920" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="921" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="922" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="923" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="924" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="925" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="926" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="927" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="928" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="929" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="930" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="931" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="932" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="933" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="934" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="935" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="936" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="937" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="938" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="939" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="940" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="941" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="942" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="943" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="944" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="945" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="946" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="947" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="948" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="949" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="950" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="951" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="952" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="953" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="954" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="955" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="956" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="957" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="958" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="959" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="960" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="961" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="962" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="963" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="964" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="965" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="966" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="967" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="968" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="969" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="970" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="971" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="972" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="973" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="974" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="975" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="976" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="977" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="978" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="979" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="980" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="981" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="982" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="983" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="984" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="985" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="986" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="987" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="988" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="989" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="990" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="991" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="992" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="993" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="994" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="995" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="996" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="997" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="998" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="999" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1000" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="33" ht="12.75" customHeight="1"/>
+    <row r="34" ht="12.75" customHeight="1"/>
+    <row r="35" ht="12.75" customHeight="1"/>
+    <row r="36" ht="12.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1"/>
+    <row r="38" ht="12.75" customHeight="1"/>
+    <row r="39" ht="12.75" customHeight="1"/>
+    <row r="40" ht="12.75" customHeight="1"/>
+    <row r="41" ht="12.75" customHeight="1"/>
+    <row r="42" ht="12.75" customHeight="1"/>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="47" ht="12.75" customHeight="1"/>
+    <row r="48" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
+  <mergeCells count="19">
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A5:C5"/>
@@ -10093,6 +9911,13 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10106,7 +9931,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J1000"/>
+  <dimension ref="A1:J994"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
@@ -10118,19 +9943,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="79" t="s">
+      <c r="B1" s="71"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="67"/>
-      <c r="F1" s="79" t="s">
+      <c r="E1" s="49"/>
+      <c r="F1" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="67"/>
+      <c r="G1" s="49"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -10142,64 +9967,64 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="61"/>
+      <c r="A2" s="73"/>
       <c r="B2" s="43"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="80" t="s">
+      <c r="C2" s="53"/>
+      <c r="D2" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="81"/>
-      <c r="F2" s="80" t="s">
+      <c r="E2" s="51"/>
+      <c r="F2" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="84">
+      <c r="G2" s="51"/>
+      <c r="H2" s="56">
         <v>46122</v>
       </c>
-      <c r="I2" s="73" t="s">
+      <c r="I2" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="76"/>
+      <c r="J2" s="60"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="61"/>
+      <c r="A3" s="73"/>
       <c r="B3" s="43"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="77"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="61"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="61"/>
+      <c r="A4" s="73"/>
       <c r="B4" s="43"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="77"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="61"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
       <c r="A5" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="90" t="s">
+      <c r="B5" s="77"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="91" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="52"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="84"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="89" t="s">
@@ -10213,22 +10038,22 @@
       <c r="G6" s="40"/>
       <c r="H6" s="40"/>
       <c r="I6" s="40"/>
-      <c r="J6" s="54"/>
+      <c r="J6" s="66"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="91"/>
-      <c r="B7" s="92"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="93"/>
+      <c r="A7" s="92"/>
+      <c r="B7" s="93"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="93"/>
+      <c r="E7" s="93"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="93"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="94"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="61"/>
+      <c r="A8" s="73"/>
       <c r="B8" s="43"/>
       <c r="C8" s="43"/>
       <c r="D8" s="43"/>
@@ -10237,10 +10062,10 @@
       <c r="G8" s="43"/>
       <c r="H8" s="43"/>
       <c r="I8" s="43"/>
-      <c r="J8" s="94"/>
+      <c r="J8" s="95"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="61"/>
+      <c r="A9" s="73"/>
       <c r="B9" s="43"/>
       <c r="C9" s="43"/>
       <c r="D9" s="43"/>
@@ -10249,10 +10074,10 @@
       <c r="G9" s="43"/>
       <c r="H9" s="43"/>
       <c r="I9" s="43"/>
-      <c r="J9" s="94"/>
+      <c r="J9" s="95"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="61"/>
+      <c r="A10" s="73"/>
       <c r="B10" s="43"/>
       <c r="C10" s="43"/>
       <c r="D10" s="43"/>
@@ -10261,10 +10086,10 @@
       <c r="G10" s="43"/>
       <c r="H10" s="43"/>
       <c r="I10" s="43"/>
-      <c r="J10" s="94"/>
+      <c r="J10" s="95"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="61"/>
+      <c r="A11" s="73"/>
       <c r="B11" s="43"/>
       <c r="C11" s="43"/>
       <c r="D11" s="43"/>
@@ -10273,10 +10098,10 @@
       <c r="G11" s="43"/>
       <c r="H11" s="43"/>
       <c r="I11" s="43"/>
-      <c r="J11" s="94"/>
+      <c r="J11" s="95"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="61"/>
+      <c r="A12" s="73"/>
       <c r="B12" s="43"/>
       <c r="C12" s="43"/>
       <c r="D12" s="43"/>
@@ -10285,10 +10110,10 @@
       <c r="G12" s="43"/>
       <c r="H12" s="43"/>
       <c r="I12" s="43"/>
-      <c r="J12" s="94"/>
+      <c r="J12" s="95"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="61"/>
+      <c r="A13" s="73"/>
       <c r="B13" s="43"/>
       <c r="C13" s="43"/>
       <c r="D13" s="43"/>
@@ -10297,7 +10122,7 @@
       <c r="G13" s="43"/>
       <c r="H13" s="43"/>
       <c r="I13" s="43"/>
-      <c r="J13" s="94"/>
+      <c r="J13" s="95"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="89" t="s">
@@ -10311,7 +10136,7 @@
       <c r="G14" s="40"/>
       <c r="H14" s="40"/>
       <c r="I14" s="40"/>
-      <c r="J14" s="54"/>
+      <c r="J14" s="66"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="89" t="s">
@@ -10319,8 +10144,8 @@
       </c>
       <c r="B15" s="40"/>
       <c r="C15" s="41"/>
-      <c r="D15" s="53" t="s">
-        <v>79</v>
+      <c r="D15" s="65" t="s">
+        <v>78</v>
       </c>
       <c r="E15" s="40"/>
       <c r="F15" s="40"/>
@@ -10330,7 +10155,7 @@
         <v>25</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
@@ -10351,104 +10176,38 @@
       <c r="G16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="95" t="s">
+      <c r="H16" s="96" t="s">
         <v>17</v>
       </c>
       <c r="I16" s="40"/>
-      <c r="J16" s="54"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="86" t="s">
+      <c r="J16" s="66"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A17" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="E17" s="17" t="s">
+      <c r="B17" s="68"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="H17" s="53"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="54"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="86"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="53"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="54"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="86"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="54"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="86"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="54"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="86"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="54"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="86"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="54"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="88"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="48"/>
-      <c r="J23" s="49"/>
-    </row>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17" s="81"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="82"/>
+    </row>
+    <row r="18" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="23" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10458,976 +10217,974 @@
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="33" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="34" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="35" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="36" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="37" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="38" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="39" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="40" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="41" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="42" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="43" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="44" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="45" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="46" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="47" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="48" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="49" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="50" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="51" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="52" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="53" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="54" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="55" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="56" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="57" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="58" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="59" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="60" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="61" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="62" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="63" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="64" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="65" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="66" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="67" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="68" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="69" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="70" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="71" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="72" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="73" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="74" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="75" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="76" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="77" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="78" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="79" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="80" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="81" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="82" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="83" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="84" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="85" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="86" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="87" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="88" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="89" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="90" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="91" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="92" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="93" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="94" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="95" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="96" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="97" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="98" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="99" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="100" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="101" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="102" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="103" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="104" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="105" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="106" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="107" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="108" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="109" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="110" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="111" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="112" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="113" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="114" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="115" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="116" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="117" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="118" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="119" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="120" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="121" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="122" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="123" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="124" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="125" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="126" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="127" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="128" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="129" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="130" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="131" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="132" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="133" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="134" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="135" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="136" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="137" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="138" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="139" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="140" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="141" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="142" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="143" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="144" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="145" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="146" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="147" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="148" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="149" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="150" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="151" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="152" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="153" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="154" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="155" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="156" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="157" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="158" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="159" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="160" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="161" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="162" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="163" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="164" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="165" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="166" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="167" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="168" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="169" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="170" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="171" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="172" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="173" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="174" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="175" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="176" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="177" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="178" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="179" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="180" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="181" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="182" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="183" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="184" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="185" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="186" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="187" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="188" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="189" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="190" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="191" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="192" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="193" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="194" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="195" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="196" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="197" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="198" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="199" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="200" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="201" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="202" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="203" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="204" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="205" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="206" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="207" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="208" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="209" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="210" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="211" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="212" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="213" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="214" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="215" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="216" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="217" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="218" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="219" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="220" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="221" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="222" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="223" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="224" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="225" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="226" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="227" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="228" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="229" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="230" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="231" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="232" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="233" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="234" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="235" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="236" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="237" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="238" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="239" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="240" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="241" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="242" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="243" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="244" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="245" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="246" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="247" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="248" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="249" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="250" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="251" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="252" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="253" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="254" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="255" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="256" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="257" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="258" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="259" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="260" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="261" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="262" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="263" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="264" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="265" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="266" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="267" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="268" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="269" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="270" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="271" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="272" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="273" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="274" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="275" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="276" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="277" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="278" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="279" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="280" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="281" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="282" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="283" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="284" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="285" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="286" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="287" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="288" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="289" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="290" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="291" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="292" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="293" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="294" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="295" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="296" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="297" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="298" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="299" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="300" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="301" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="302" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="303" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="304" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="305" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="306" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="307" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="308" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="309" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="310" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="311" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="312" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="313" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="314" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="315" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="316" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="317" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="318" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="319" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="320" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="321" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="322" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="323" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="324" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="325" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="326" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="327" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="328" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="329" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="330" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="331" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="332" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="333" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="334" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="335" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="336" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="337" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="338" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="339" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="340" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="341" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="342" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="343" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="344" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="345" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="346" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="347" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="348" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="349" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="350" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="351" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="352" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="353" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="354" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="355" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="356" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="357" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="358" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="359" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="360" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="361" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="362" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="363" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="364" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="365" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="366" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="367" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="368" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="369" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="370" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="371" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="372" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="373" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="374" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="375" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="376" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="377" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="378" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="379" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="380" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="381" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="382" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="383" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="384" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="385" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="386" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="387" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="388" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="389" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="390" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="391" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="392" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="393" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="394" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="395" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="396" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="397" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="398" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="399" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="400" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="401" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="402" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="403" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="404" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="405" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="406" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="407" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="408" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="409" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="410" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="411" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="412" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="413" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="414" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="415" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="416" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="417" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="418" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="419" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="420" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="421" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="422" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="423" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="424" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="425" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="426" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="427" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="428" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="429" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="430" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="431" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="432" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="433" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="434" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="435" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="436" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="437" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="438" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="439" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="440" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="441" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="442" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="443" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="444" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="445" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="446" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="447" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="448" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="449" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="450" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="451" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="452" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="453" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="454" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="455" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="456" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="457" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="458" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="459" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="460" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="461" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="462" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="463" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="464" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="465" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="466" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="467" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="468" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="469" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="470" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="471" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="472" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="473" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="474" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="475" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="476" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="477" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="478" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="479" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="480" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="481" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="482" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="483" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="484" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="485" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="486" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="487" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="488" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="489" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="490" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="491" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="492" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="493" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="494" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="495" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="496" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="497" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="498" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="499" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="500" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="501" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="502" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="503" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="504" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="505" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="506" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="507" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="508" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="509" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="510" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="511" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="512" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="513" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="514" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="515" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="516" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="517" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="518" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="519" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="520" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="521" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="522" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="523" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="524" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="525" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="526" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="527" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="528" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="529" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="530" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="531" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="532" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="533" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="534" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="535" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="536" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="537" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="538" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="539" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="540" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="541" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="542" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="543" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="544" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="545" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="546" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="547" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="548" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="549" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="550" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="551" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="552" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="553" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="554" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="555" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="556" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="557" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="558" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="559" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="560" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="561" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="562" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="563" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="564" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="565" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="566" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="567" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="568" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="569" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="570" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="571" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="572" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="573" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="574" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="575" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="576" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="577" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="578" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="579" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="580" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="581" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="582" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="583" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="584" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="585" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="586" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="587" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="588" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="589" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="590" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="591" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="592" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="593" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="594" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="595" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="596" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="597" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="598" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="599" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="600" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="601" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="602" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="603" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="604" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="605" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="606" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="607" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="608" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="609" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="610" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="611" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="612" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="613" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="614" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="615" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="616" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="617" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="618" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="619" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="620" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="621" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="622" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="623" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="624" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="625" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="626" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="627" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="628" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="629" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="630" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="631" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="632" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="633" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="634" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="635" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="636" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="637" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="638" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="639" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="640" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="641" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="642" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="643" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="644" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="645" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="646" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="647" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="648" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="649" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="650" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="651" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="652" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="653" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="654" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="655" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="656" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="657" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="658" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="659" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="660" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="661" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="662" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="663" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="664" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="665" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="666" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="667" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="668" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="669" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="670" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="671" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="672" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="673" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="674" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="675" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="676" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="677" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="678" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="679" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="680" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="681" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="682" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="683" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="684" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="685" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="686" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="687" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="688" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="689" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="690" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="691" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="692" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="693" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="694" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="695" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="696" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="697" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="698" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="699" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="700" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="701" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="702" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="703" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="704" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="705" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="706" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="707" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="708" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="709" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="710" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="711" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="712" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="713" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="714" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="715" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="716" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="717" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="718" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="719" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="720" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="721" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="722" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="723" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="724" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="725" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="726" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="727" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="728" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="729" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="730" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="731" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="732" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="733" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="734" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="735" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="736" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="737" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="738" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="739" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="740" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="741" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="742" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="743" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="744" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="745" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="746" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="747" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="748" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="749" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="750" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="751" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="752" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="753" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="754" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="755" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="756" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="757" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="758" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="759" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="760" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="761" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="762" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="763" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="764" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="765" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="766" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="767" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="768" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="769" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="770" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="771" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="772" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="773" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="774" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="775" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="776" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="777" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="778" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="779" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="780" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="781" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="782" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="783" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="784" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="785" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="786" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="787" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="788" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="789" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="790" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="791" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="792" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="793" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="794" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="795" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="796" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="797" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="798" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="799" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="800" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="801" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="802" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="803" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="804" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="805" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="806" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="807" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="808" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="809" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="810" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="811" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="812" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="813" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="814" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="815" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="816" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="817" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="818" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="819" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="820" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="821" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="822" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="823" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="824" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="825" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="826" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="827" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="828" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="829" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="830" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="831" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="832" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="833" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="834" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="835" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="836" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="837" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="838" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="839" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="840" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="841" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="842" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="843" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="844" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="845" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="846" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="847" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="848" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="849" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="850" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="851" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="852" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="853" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="854" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="855" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="856" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="857" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="858" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="859" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="860" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="861" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="862" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="863" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="864" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="865" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="866" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="867" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="868" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="869" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="870" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="871" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="872" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="873" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="874" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="875" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="876" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="877" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="878" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="879" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="880" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="881" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="882" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="883" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="884" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="885" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="886" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="887" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="888" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="889" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="890" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="891" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="892" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="893" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="894" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="895" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="896" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="897" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="898" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="899" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="900" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="901" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="902" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="903" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="904" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="905" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="906" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="907" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="908" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="909" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="910" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="911" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="912" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="913" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="914" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="915" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="916" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="917" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="918" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="919" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="920" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="921" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="922" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="923" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="924" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="925" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="926" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="927" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="928" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="929" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="930" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="931" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="932" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="933" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="934" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="935" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="936" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="937" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="938" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="939" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="940" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="941" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="942" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="943" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="944" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="945" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="946" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="947" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="948" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="949" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="950" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="951" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="952" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="953" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="954" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="955" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="956" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="957" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="958" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="959" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="960" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="961" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="962" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="963" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="964" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="965" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="966" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="967" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="968" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="969" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="970" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="971" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="972" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="973" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="974" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="975" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="976" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="977" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="978" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="979" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="980" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="981" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="982" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="983" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="984" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="985" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="986" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="987" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="988" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="989" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="990" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="991" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="992" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="993" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="994" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="995" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="996" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="997" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="998" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="999" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="1000" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="33" ht="12.75" customHeight="1"/>
+    <row r="34" ht="12.75" customHeight="1"/>
+    <row r="35" ht="12.75" customHeight="1"/>
+    <row r="36" ht="12.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1"/>
+    <row r="38" ht="12.75" customHeight="1"/>
+    <row r="39" ht="12.75" customHeight="1"/>
+    <row r="40" ht="12.75" customHeight="1"/>
+    <row r="41" ht="12.75" customHeight="1"/>
+    <row r="42" ht="12.75" customHeight="1"/>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="47" ht="12.75" customHeight="1"/>
+    <row r="48" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="19">
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -11443,22 +11200,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11478,130 +11219,130 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="79" t="s">
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="79" t="s">
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="79" t="s">
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="79" t="s">
+      <c r="P1" s="49"/>
+      <c r="Q1" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="67"/>
-      <c r="S1" s="79" t="s">
+      <c r="R1" s="49"/>
+      <c r="S1" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="52"/>
+      <c r="T1" s="84"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="61"/>
+      <c r="A2" s="73"/>
       <c r="B2" s="43"/>
       <c r="C2" s="43"/>
       <c r="D2" s="43"/>
       <c r="E2" s="43"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="80"/>
-      <c r="P2" s="81"/>
-      <c r="Q2" s="80"/>
-      <c r="R2" s="81"/>
-      <c r="S2" s="80"/>
-      <c r="T2" s="93"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="93"/>
+      <c r="M2" s="93"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="50"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="50"/>
+      <c r="T2" s="94"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="61"/>
+      <c r="A3" s="73"/>
       <c r="B3" s="43"/>
       <c r="C3" s="43"/>
       <c r="D3" s="43"/>
       <c r="E3" s="43"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="82"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="52"/>
       <c r="H3" s="43"/>
       <c r="I3" s="43"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="82"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="52"/>
       <c r="L3" s="43"/>
       <c r="M3" s="43"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="82"/>
-      <c r="P3" s="62"/>
-      <c r="Q3" s="82"/>
-      <c r="R3" s="62"/>
-      <c r="S3" s="82"/>
-      <c r="T3" s="94"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="52"/>
+      <c r="P3" s="53"/>
+      <c r="Q3" s="52"/>
+      <c r="R3" s="53"/>
+      <c r="S3" s="52"/>
+      <c r="T3" s="95"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="104"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="75"/>
+      <c r="M4" s="75"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="55"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="55"/>
+      <c r="S4" s="54"/>
+      <c r="T4" s="101"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
       <c r="A5" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="50" t="s">
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="51"/>
-      <c r="N5" s="51"/>
-      <c r="O5" s="51"/>
-      <c r="P5" s="51"/>
-      <c r="Q5" s="51"/>
-      <c r="R5" s="51"/>
-      <c r="S5" s="51"/>
-      <c r="T5" s="52"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="77"/>
+      <c r="M5" s="77"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="77"/>
+      <c r="S5" s="77"/>
+      <c r="T5" s="84"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
       <c r="A6" s="89" t="s">
@@ -11612,7 +11353,7 @@
       <c r="D6" s="40"/>
       <c r="E6" s="40"/>
       <c r="F6" s="41"/>
-      <c r="G6" s="53" t="s">
+      <c r="G6" s="65" t="s">
         <v>18</v>
       </c>
       <c r="H6" s="40"/>
@@ -11627,7 +11368,7 @@
       <c r="Q6" s="40"/>
       <c r="R6" s="40"/>
       <c r="S6" s="40"/>
-      <c r="T6" s="54"/>
+      <c r="T6" s="66"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
       <c r="A7" s="89" t="s">
@@ -11638,7 +11379,7 @@
       <c r="D7" s="40"/>
       <c r="E7" s="40"/>
       <c r="F7" s="41"/>
-      <c r="G7" s="53" t="s">
+      <c r="G7" s="65" t="s">
         <v>36</v>
       </c>
       <c r="H7" s="40"/>
@@ -11653,7 +11394,7 @@
       <c r="Q7" s="40"/>
       <c r="R7" s="40"/>
       <c r="S7" s="40"/>
-      <c r="T7" s="54"/>
+      <c r="T7" s="66"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -11856,29 +11597,29 @@
         <v>43</v>
       </c>
       <c r="B15" s="41"/>
-      <c r="C15" s="103" t="s">
+      <c r="C15" s="104" t="s">
         <v>37</v>
       </c>
       <c r="D15" s="41"/>
-      <c r="E15" s="95" t="s">
+      <c r="E15" s="96" t="s">
         <v>44</v>
       </c>
       <c r="F15" s="41"/>
-      <c r="G15" s="95" t="s">
+      <c r="G15" s="96" t="s">
         <v>45</v>
       </c>
       <c r="H15" s="40"/>
       <c r="I15" s="41"/>
-      <c r="J15" s="95" t="s">
+      <c r="J15" s="96" t="s">
         <v>46</v>
       </c>
       <c r="K15" s="41"/>
-      <c r="L15" s="95" t="s">
+      <c r="L15" s="96" t="s">
         <v>47</v>
       </c>
       <c r="M15" s="40"/>
       <c r="N15" s="41"/>
-      <c r="O15" s="95" t="s">
+      <c r="O15" s="96" t="s">
         <v>48</v>
       </c>
       <c r="P15" s="40"/>
@@ -11894,33 +11635,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="96">
+      <c r="A16" s="102">
         <v>1</v>
       </c>
       <c r="B16" s="41"/>
-      <c r="C16" s="97" t="s">
+      <c r="C16" s="103" t="s">
         <v>52</v>
       </c>
       <c r="D16" s="41"/>
-      <c r="E16" s="97" t="s">
+      <c r="E16" s="103" t="s">
         <v>53</v>
       </c>
       <c r="F16" s="41"/>
-      <c r="G16" s="102" t="s">
+      <c r="G16" s="97" t="s">
         <v>54</v>
       </c>
       <c r="H16" s="40"/>
       <c r="I16" s="41"/>
-      <c r="J16" s="102" t="s">
+      <c r="J16" s="97" t="s">
         <v>55</v>
       </c>
       <c r="K16" s="41"/>
-      <c r="L16" s="100" t="s">
+      <c r="L16" s="99" t="s">
         <v>56</v>
       </c>
       <c r="M16" s="40"/>
       <c r="N16" s="41"/>
-      <c r="O16" s="100" t="s">
+      <c r="O16" s="99" t="s">
         <v>57</v>
       </c>
       <c r="P16" s="40"/>
@@ -11936,33 +11677,33 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="96">
+      <c r="A17" s="102">
         <v>2</v>
       </c>
       <c r="B17" s="41"/>
-      <c r="C17" s="97" t="s">
+      <c r="C17" s="103" t="s">
         <v>58</v>
       </c>
       <c r="D17" s="41"/>
-      <c r="E17" s="97" t="s">
+      <c r="E17" s="103" t="s">
         <v>59</v>
       </c>
       <c r="F17" s="41"/>
-      <c r="G17" s="102" t="s">
+      <c r="G17" s="97" t="s">
         <v>60</v>
       </c>
       <c r="H17" s="40"/>
       <c r="I17" s="41"/>
-      <c r="J17" s="102" t="s">
+      <c r="J17" s="97" t="s">
         <v>61</v>
       </c>
       <c r="K17" s="41"/>
-      <c r="L17" s="100" t="s">
+      <c r="L17" s="99" t="s">
         <v>62</v>
       </c>
       <c r="M17" s="40"/>
       <c r="N17" s="41"/>
-      <c r="O17" s="100" t="s">
+      <c r="O17" s="99" t="s">
         <v>63</v>
       </c>
       <c r="P17" s="40"/>
@@ -11978,21 +11719,21 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="96"/>
+      <c r="A18" s="102"/>
       <c r="B18" s="41"/>
-      <c r="C18" s="97"/>
+      <c r="C18" s="103"/>
       <c r="D18" s="41"/>
-      <c r="E18" s="97"/>
+      <c r="E18" s="103"/>
       <c r="F18" s="41"/>
-      <c r="G18" s="102"/>
+      <c r="G18" s="97"/>
       <c r="H18" s="40"/>
       <c r="I18" s="41"/>
-      <c r="J18" s="102"/>
+      <c r="J18" s="97"/>
       <c r="K18" s="41"/>
-      <c r="L18" s="100"/>
+      <c r="L18" s="99"/>
       <c r="M18" s="40"/>
       <c r="N18" s="41"/>
-      <c r="O18" s="100"/>
+      <c r="O18" s="99"/>
       <c r="P18" s="40"/>
       <c r="Q18" s="41"/>
       <c r="R18" s="33"/>
@@ -12006,21 +11747,21 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="96"/>
+      <c r="A19" s="102"/>
       <c r="B19" s="41"/>
-      <c r="C19" s="97"/>
+      <c r="C19" s="103"/>
       <c r="D19" s="41"/>
-      <c r="E19" s="97"/>
+      <c r="E19" s="103"/>
       <c r="F19" s="41"/>
-      <c r="G19" s="102"/>
+      <c r="G19" s="97"/>
       <c r="H19" s="40"/>
       <c r="I19" s="41"/>
-      <c r="J19" s="102"/>
+      <c r="J19" s="97"/>
       <c r="K19" s="41"/>
-      <c r="L19" s="100"/>
+      <c r="L19" s="99"/>
       <c r="M19" s="40"/>
       <c r="N19" s="41"/>
-      <c r="O19" s="100"/>
+      <c r="O19" s="99"/>
       <c r="P19" s="40"/>
       <c r="Q19" s="41"/>
       <c r="R19" s="33"/>
@@ -12034,21 +11775,21 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="96"/>
+      <c r="A20" s="102"/>
       <c r="B20" s="41"/>
-      <c r="C20" s="97"/>
+      <c r="C20" s="103"/>
       <c r="D20" s="41"/>
-      <c r="E20" s="97"/>
+      <c r="E20" s="103"/>
       <c r="F20" s="41"/>
-      <c r="G20" s="102"/>
+      <c r="G20" s="97"/>
       <c r="H20" s="40"/>
       <c r="I20" s="41"/>
-      <c r="J20" s="102"/>
+      <c r="J20" s="97"/>
       <c r="K20" s="41"/>
-      <c r="L20" s="100"/>
+      <c r="L20" s="99"/>
       <c r="M20" s="40"/>
       <c r="N20" s="41"/>
-      <c r="O20" s="100"/>
+      <c r="O20" s="99"/>
       <c r="P20" s="40"/>
       <c r="Q20" s="41"/>
       <c r="R20" s="33"/>
@@ -12062,21 +11803,21 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="96"/>
+      <c r="A21" s="102"/>
       <c r="B21" s="41"/>
-      <c r="C21" s="97"/>
+      <c r="C21" s="103"/>
       <c r="D21" s="41"/>
-      <c r="E21" s="97"/>
+      <c r="E21" s="103"/>
       <c r="F21" s="41"/>
-      <c r="G21" s="102"/>
+      <c r="G21" s="97"/>
       <c r="H21" s="40"/>
       <c r="I21" s="41"/>
-      <c r="J21" s="102"/>
+      <c r="J21" s="97"/>
       <c r="K21" s="41"/>
-      <c r="L21" s="100"/>
+      <c r="L21" s="99"/>
       <c r="M21" s="40"/>
       <c r="N21" s="41"/>
-      <c r="O21" s="100"/>
+      <c r="O21" s="99"/>
       <c r="P21" s="40"/>
       <c r="Q21" s="41"/>
       <c r="R21" s="33"/>
@@ -12090,21 +11831,21 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="96"/>
+      <c r="A22" s="102"/>
       <c r="B22" s="41"/>
-      <c r="C22" s="97"/>
+      <c r="C22" s="103"/>
       <c r="D22" s="41"/>
-      <c r="E22" s="97"/>
+      <c r="E22" s="103"/>
       <c r="F22" s="41"/>
-      <c r="G22" s="102"/>
+      <c r="G22" s="97"/>
       <c r="H22" s="40"/>
       <c r="I22" s="41"/>
-      <c r="J22" s="102"/>
+      <c r="J22" s="97"/>
       <c r="K22" s="41"/>
-      <c r="L22" s="100"/>
+      <c r="L22" s="99"/>
       <c r="M22" s="40"/>
       <c r="N22" s="41"/>
-      <c r="O22" s="100"/>
+      <c r="O22" s="99"/>
       <c r="P22" s="40"/>
       <c r="Q22" s="41"/>
       <c r="R22" s="33"/>
@@ -12118,21 +11859,21 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="96"/>
+      <c r="A23" s="102"/>
       <c r="B23" s="41"/>
-      <c r="C23" s="97"/>
+      <c r="C23" s="103"/>
       <c r="D23" s="41"/>
-      <c r="E23" s="97"/>
+      <c r="E23" s="103"/>
       <c r="F23" s="41"/>
-      <c r="G23" s="102"/>
+      <c r="G23" s="97"/>
       <c r="H23" s="40"/>
       <c r="I23" s="41"/>
-      <c r="J23" s="102"/>
+      <c r="J23" s="97"/>
       <c r="K23" s="41"/>
-      <c r="L23" s="100"/>
+      <c r="L23" s="99"/>
       <c r="M23" s="40"/>
       <c r="N23" s="41"/>
-      <c r="O23" s="100"/>
+      <c r="O23" s="99"/>
       <c r="P23" s="40"/>
       <c r="Q23" s="41"/>
       <c r="R23" s="33"/>
@@ -12146,21 +11887,21 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="96"/>
+      <c r="A24" s="102"/>
       <c r="B24" s="41"/>
-      <c r="C24" s="97"/>
+      <c r="C24" s="103"/>
       <c r="D24" s="41"/>
-      <c r="E24" s="97"/>
+      <c r="E24" s="103"/>
       <c r="F24" s="41"/>
-      <c r="G24" s="102"/>
+      <c r="G24" s="97"/>
       <c r="H24" s="40"/>
       <c r="I24" s="41"/>
-      <c r="J24" s="102"/>
+      <c r="J24" s="97"/>
       <c r="K24" s="41"/>
-      <c r="L24" s="100"/>
+      <c r="L24" s="99"/>
       <c r="M24" s="40"/>
       <c r="N24" s="41"/>
-      <c r="O24" s="100"/>
+      <c r="O24" s="99"/>
       <c r="P24" s="40"/>
       <c r="Q24" s="41"/>
       <c r="R24" s="33"/>
@@ -12174,21 +11915,21 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="96"/>
+      <c r="A25" s="102"/>
       <c r="B25" s="41"/>
-      <c r="C25" s="97"/>
+      <c r="C25" s="103"/>
       <c r="D25" s="41"/>
-      <c r="E25" s="97"/>
+      <c r="E25" s="103"/>
       <c r="F25" s="41"/>
-      <c r="G25" s="102"/>
+      <c r="G25" s="97"/>
       <c r="H25" s="40"/>
       <c r="I25" s="41"/>
-      <c r="J25" s="102"/>
+      <c r="J25" s="97"/>
       <c r="K25" s="41"/>
-      <c r="L25" s="100"/>
+      <c r="L25" s="99"/>
       <c r="M25" s="40"/>
       <c r="N25" s="41"/>
-      <c r="O25" s="100"/>
+      <c r="O25" s="99"/>
       <c r="P25" s="40"/>
       <c r="Q25" s="41"/>
       <c r="R25" s="33"/>
@@ -12202,21 +11943,21 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="96"/>
+      <c r="A26" s="102"/>
       <c r="B26" s="41"/>
-      <c r="C26" s="97"/>
+      <c r="C26" s="103"/>
       <c r="D26" s="41"/>
-      <c r="E26" s="97"/>
+      <c r="E26" s="103"/>
       <c r="F26" s="41"/>
-      <c r="G26" s="102"/>
+      <c r="G26" s="97"/>
       <c r="H26" s="40"/>
       <c r="I26" s="41"/>
-      <c r="J26" s="102"/>
+      <c r="J26" s="97"/>
       <c r="K26" s="41"/>
-      <c r="L26" s="100"/>
+      <c r="L26" s="99"/>
       <c r="M26" s="40"/>
       <c r="N26" s="41"/>
-      <c r="O26" s="100"/>
+      <c r="O26" s="99"/>
       <c r="P26" s="40"/>
       <c r="Q26" s="41"/>
       <c r="R26" s="33"/>
@@ -12230,21 +11971,21 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="96"/>
+      <c r="A27" s="102"/>
       <c r="B27" s="41"/>
-      <c r="C27" s="97"/>
+      <c r="C27" s="103"/>
       <c r="D27" s="41"/>
-      <c r="E27" s="97"/>
+      <c r="E27" s="103"/>
       <c r="F27" s="41"/>
-      <c r="G27" s="102"/>
+      <c r="G27" s="97"/>
       <c r="H27" s="40"/>
       <c r="I27" s="41"/>
-      <c r="J27" s="102"/>
+      <c r="J27" s="97"/>
       <c r="K27" s="41"/>
-      <c r="L27" s="100"/>
+      <c r="L27" s="99"/>
       <c r="M27" s="40"/>
       <c r="N27" s="41"/>
-      <c r="O27" s="100"/>
+      <c r="O27" s="99"/>
       <c r="P27" s="40"/>
       <c r="Q27" s="41"/>
       <c r="R27" s="33"/>
@@ -12258,21 +11999,21 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="96"/>
+      <c r="A28" s="102"/>
       <c r="B28" s="41"/>
-      <c r="C28" s="97"/>
+      <c r="C28" s="103"/>
       <c r="D28" s="41"/>
-      <c r="E28" s="97"/>
+      <c r="E28" s="103"/>
       <c r="F28" s="41"/>
-      <c r="G28" s="102"/>
+      <c r="G28" s="97"/>
       <c r="H28" s="40"/>
       <c r="I28" s="41"/>
-      <c r="J28" s="102"/>
+      <c r="J28" s="97"/>
       <c r="K28" s="41"/>
-      <c r="L28" s="100"/>
+      <c r="L28" s="99"/>
       <c r="M28" s="40"/>
       <c r="N28" s="41"/>
-      <c r="O28" s="100"/>
+      <c r="O28" s="99"/>
       <c r="P28" s="40"/>
       <c r="Q28" s="41"/>
       <c r="R28" s="33"/>
@@ -12286,21 +12027,21 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="96"/>
+      <c r="A29" s="102"/>
       <c r="B29" s="41"/>
-      <c r="C29" s="97"/>
+      <c r="C29" s="103"/>
       <c r="D29" s="41"/>
-      <c r="E29" s="97"/>
+      <c r="E29" s="103"/>
       <c r="F29" s="41"/>
-      <c r="G29" s="102"/>
+      <c r="G29" s="97"/>
       <c r="H29" s="40"/>
       <c r="I29" s="41"/>
-      <c r="J29" s="102"/>
+      <c r="J29" s="97"/>
       <c r="K29" s="41"/>
-      <c r="L29" s="100"/>
+      <c r="L29" s="99"/>
       <c r="M29" s="40"/>
       <c r="N29" s="41"/>
-      <c r="O29" s="100"/>
+      <c r="O29" s="99"/>
       <c r="P29" s="40"/>
       <c r="Q29" s="41"/>
       <c r="R29" s="33"/>
@@ -12314,21 +12055,21 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="96"/>
+      <c r="A30" s="102"/>
       <c r="B30" s="41"/>
-      <c r="C30" s="97"/>
+      <c r="C30" s="103"/>
       <c r="D30" s="41"/>
-      <c r="E30" s="97"/>
+      <c r="E30" s="103"/>
       <c r="F30" s="41"/>
-      <c r="G30" s="102"/>
+      <c r="G30" s="97"/>
       <c r="H30" s="40"/>
       <c r="I30" s="41"/>
-      <c r="J30" s="102"/>
+      <c r="J30" s="97"/>
       <c r="K30" s="41"/>
-      <c r="L30" s="100"/>
+      <c r="L30" s="99"/>
       <c r="M30" s="40"/>
       <c r="N30" s="41"/>
-      <c r="O30" s="100"/>
+      <c r="O30" s="99"/>
       <c r="P30" s="40"/>
       <c r="Q30" s="41"/>
       <c r="R30" s="33"/>
@@ -12342,23 +12083,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="98"/>
-      <c r="B31" s="57"/>
-      <c r="C31" s="99"/>
-      <c r="D31" s="57"/>
-      <c r="E31" s="99"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="105"/>
-      <c r="H31" s="48"/>
-      <c r="I31" s="57"/>
-      <c r="J31" s="105"/>
-      <c r="K31" s="57"/>
-      <c r="L31" s="101"/>
-      <c r="M31" s="48"/>
-      <c r="N31" s="57"/>
-      <c r="O31" s="101"/>
-      <c r="P31" s="48"/>
-      <c r="Q31" s="57"/>
+      <c r="A31" s="105"/>
+      <c r="B31" s="69"/>
+      <c r="C31" s="106"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="106"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="98"/>
+      <c r="H31" s="68"/>
+      <c r="I31" s="69"/>
+      <c r="J31" s="98"/>
+      <c r="K31" s="69"/>
+      <c r="L31" s="100"/>
+      <c r="M31" s="68"/>
+      <c r="N31" s="69"/>
+      <c r="O31" s="100"/>
+      <c r="P31" s="68"/>
+      <c r="Q31" s="69"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -13356,62 +13097,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -13436,62 +13177,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
